--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,33 +988,33 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>564572.4</t>
+          <t>648147.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>201223.44</t>
+          <t>212611.62</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>81925.84</v>
+        <v>83071.92999999999</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>454356.8</t>
+          <t>564572.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>191580.74</t>
+          <t>201223.44</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>78358.95</v>
+        <v>81925.84</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,22 +1608,22 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,74 +1755,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>321219.0</t>
+          <t>454356.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>176809.8</t>
+          <t>191580.74</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>49373.9</v>
+        <v>78358.95</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,27 +2039,27 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10661.0</t>
+          <t>12008.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,33 +2281,33 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>96.03</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-76.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>551491.0</t>
+          <t>681031.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>227054.6</t>
+          <t>321219.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>234174.7</t>
+          <t>255754.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>164471.06</t>
+          <t>176809.8</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-7120</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1655.564760526683</t>
+          <t>6195.122263684315</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>18686.23</v>
+        <v>49373.9</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>10661.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-68.02</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-77.68</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>192113.0</t>
+          <t>551491.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>138115.6</t>
+          <t>227054.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>190650.3</t>
+          <t>234174.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>155068.52</t>
+          <t>164471.06</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-52534</t>
+          <t>-7120</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5354.072467350683</t>
+          <t>-1655.564760526683</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-11941.39</v>
+        <v>18686.23</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1057.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-71.34</t>
+          <t>-68.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-73.89</t>
+          <t>-77.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>49611.0</t>
+          <t>192113.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>150739.6</t>
+          <t>138115.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>183244.8</t>
+          <t>190650.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>154161.68</t>
+          <t>155068.52</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-32505</t>
+          <t>-52534</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4156.379248009005</t>
+          <t>-5354.072467350683</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-16763.85</v>
+        <v>-11941.39</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2745.0</t>
+          <t>1057.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-17.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>51.09</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-63.27</t>
+          <t>-71.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-73.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>131849.0</t>
+          <t>49611.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>175806.2</t>
+          <t>150739.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>186429.5</t>
+          <t>183244.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>156017.42</t>
+          <t>154161.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-10623</t>
+          <t>-32505</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1864.111113100804</t>
+          <t>-4156.379248009005</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-7786.31</v>
+        <v>-16763.85</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4338.0</t>
+          <t>2745.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,37 +4026,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.66</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>51.17</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-60.34</t>
+          <t>-63.27</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-64.37</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>210209.0</t>
+          <t>131849.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>190290.2</t>
+          <t>175806.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>178505.4</t>
+          <t>186429.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>154783.0</t>
+          <t>156017.42</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>-10623</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-787.3468324887472</t>
+          <t>-1864.111113100804</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-3494.39</v>
+        <v>-7786.31</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2239.0</t>
+          <t>4338.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.48</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-64.41</t>
+          <t>-60.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-58.99</t>
+          <t>-64.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>106796.0</t>
+          <t>210209.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>241294.8</t>
+          <t>190290.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>166253.2</t>
+          <t>178505.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>152073.08</t>
+          <t>154783.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>75041</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-295.1571501936293</t>
+          <t>-787.3468324887472</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-5633.98</v>
+        <v>-3494.39</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5279.0</t>
+          <t>2239.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.49</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-61.80</t>
+          <t>-64.41</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-58.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>255233.0</t>
+          <t>106796.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>243185.0</t>
+          <t>241294.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>169332.6</t>
+          <t>166253.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>153829.38</t>
+          <t>152073.08</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>73852</t>
+          <t>75041</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>675.538624081627</t>
+          <t>-295.1571501936293</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>2590.63</v>
+        <v>-5633.98</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3760.0</t>
+          <t>5279.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>13.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.56</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>50.87</t>
+          <t>51.09</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-59.05</t>
+          <t>-61.80</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-45.03</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75504.22141823445</t>
+          <t>76717.33959537571</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>174944.0</t>
+          <t>255233.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>215750.0</t>
+          <t>243185.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>159661.8</t>
+          <t>169332.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>153778.54</t>
+          <t>153829.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>56088</t>
+          <t>73852</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>327.3399224791324</t>
+          <t>675.538624081627</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1656.4</v>
+        <v>2590.63</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>21.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-14.19756084958449</t>
+          <t>-4.142025122335156</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>12.88533205243801</t>
+          <t>31.9210612054922</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>58.40118400615614</t>
+          <t>52.5841306079603</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,42 +5619,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-3.61</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6416.499</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3558.4</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>633.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,17 +5770,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5790,37 +5790,37 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>678.2</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>677.46</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>3110892215.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>2089597881.18</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>184622942.89</v>
+        <v>272741488.12</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,27 +5918,27 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>681.95</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>677.64</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>2660675287.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>2031062259.28</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>236195769.4</v>
+        <v>184622942.89</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6349,32 +6349,32 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,17 +6434,17 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>684.55</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>677.36</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>2688233856.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>2012331643.46</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>194429357.4</v>
+        <v>236195769.4</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,22 +6780,22 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>6078.152</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>663.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>687.1</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>677.34</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>666.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-676.47</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-95.91</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>3950855603.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>2444767042.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>2195634921.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1973519631.2</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>249132120</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>33785075.45068976</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>52995513.02</v>
+        <v>194429357.4</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,42 +7211,42 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2587.128</t>
+          <t>3200.569</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>690.9</t>
+          <t>689.1</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>676.56</t>
+          <t>677.08</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>665.72</t>
+          <t>666.05</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-133.28</t>
+          <t>-219.00</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-88.98</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1720492718.0</t>
+          <t>2125750388.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2044328041.6</t>
+          <t>2117069946.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1858898579.5</t>
+          <t>1936357091.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1901243274.0</t>
+          <t>1916414460.46</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>185429462</t>
+          <t>180712855</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4226337.417336328</t>
+          <t>4577024.187966792</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>44601454.33</v>
+        <v>52995513.02</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,27 +7642,27 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>662.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3583.582</t>
+          <t>2587.128</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>691.6</t>
+          <t>690.9</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>676.06</t>
+          <t>676.56</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>665.44</t>
+          <t>665.72</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-133.28</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-82.95</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2391568906.0</t>
+          <t>1720492718.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2129942802.4</t>
+          <t>2044328041.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1937240022.2</t>
+          <t>1858898579.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1893640408.06</t>
+          <t>1901243274.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>192702780</t>
+          <t>185429462</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-13104117.73556212</t>
+          <t>-4226337.417336328</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>74437497.48999999</v>
+        <v>44601454.33</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,42 +8073,42 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>662.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>664.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2990.66</t>
+          <t>3583.582</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>687.6</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>691.6</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>675.44</t>
+          <t>676.06</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>665.02</t>
+          <t>665.44</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-50.69</t>
+          <t>-86.71</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-72.34</t>
+          <t>-77.27</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2035167596.0</t>
+          <t>2391568906.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2018014894.0</t>
+          <t>2129942802.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1817621011.7</t>
+          <t>1937240022.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1870325126.16</t>
+          <t>1893640408.06</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>200393882</t>
+          <t>192702780</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-29020775.04864686</t>
+          <t>-13104117.73556212</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>42500914.08</v>
+        <v>74437497.48999999</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,42 +8504,42 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3424.467</t>
+          <t>2990.66</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>693.2</t>
+          <t>687.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>693.5</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>674.24</t>
+          <t>675.44</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>664.54</t>
+          <t>665.02</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-37.33</t>
+          <t>-50.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-68.83</t>
+          <t>-72.34</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2312370123.0</t>
+          <t>2035167596.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1946502801.0</t>
+          <t>2018014894.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1695217335.8</t>
+          <t>1817621011.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1857410869.06</t>
+          <t>1870325126.16</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>251285465</t>
+          <t>200393882</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-42024718.52679587</t>
+          <t>-29020775.04864686</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>33545188.36</v>
+        <v>42500914.08</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8935,32 +8935,32 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,17 +9020,17 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>666.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2544.205</t>
+          <t>3424.467</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>693.2</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>693.7</t>
+          <t>693.5</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>673.14</t>
+          <t>674.24</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>664.05</t>
+          <t>664.54</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-21.44</t>
+          <t>-37.33</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-65.92</t>
+          <t>-68.83</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1762040865.0</t>
+          <t>2312370123.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1755644235.8</t>
+          <t>1946502801.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1570290079.0</t>
+          <t>1695217335.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1841151084.92</t>
+          <t>1857410869.06</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>185354156</t>
+          <t>251285465</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-55764701.59648874</t>
+          <t>-42024718.52679587</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-10147018.73</v>
+        <v>33545188.36</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,27 +9366,27 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>666.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3097.185</t>
+          <t>2544.205</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,72 +9513,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>688.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-12.79</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-9.16</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-3.08</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>7.90</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>714.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>691.0</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>693.5</t>
+          <t>693.7</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>671.88</t>
+          <t>673.14</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>663.46</t>
+          <t>664.05</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-21.44</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-64.10</t>
+          <t>-65.92</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2148566522.0</t>
+          <t>1762040865.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1673469117.4</t>
+          <t>1755644235.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1550878924.7</t>
+          <t>1570290079.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1859076743.5</t>
+          <t>1841151084.92</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>122590192</t>
+          <t>185354156</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-64058825.754549</t>
+          <t>-55764701.59648874</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-13238214.82</v>
+        <v>-10147018.73</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>702.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2617.669</t>
+          <t>3097.185</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>697.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.11</t>
+          <t>-13.28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>707.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>692.75</t>
+          <t>693.5</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>670.72</t>
+          <t>671.88</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>663.46</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-63.26</t>
+          <t>-64.10</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3294288569.837193</t>
+          <t>3298136947.677745</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1831929364.0</t>
+          <t>2148566522.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1744537242.0</t>
+          <t>1673469117.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1459488686.9</t>
+          <t>1550878924.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1846423402.46</t>
+          <t>1859076743.5</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>285048555</t>
+          <t>122590192</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-73298936.83342709</t>
+          <t>-64058825.754549</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-58594879.1</v>
+        <v>-13238214.82</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>14.47783733669335</t>
+          <t>-19.69180399575732</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>9.932930835391057</t>
+          <t>32.8429209193585</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>22.18272860341227</t>
+          <t>24.67740643280432</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>470167</t>
+          <t>453084</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>702.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>697.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>697.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>648147.4</t>
+          <t>609252.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>212611.62</t>
+          <t>218290.42</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>83071.92999999999</v>
+        <v>62824.5</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,33 +1419,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>564572.4</t>
+          <t>648147.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>201223.44</t>
+          <t>212611.62</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>81925.84</v>
+        <v>83071.92999999999</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>454356.8</t>
+          <t>564572.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>191580.74</t>
+          <t>201223.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>78358.95</v>
+        <v>81925.84</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,74 +2186,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>321219.0</t>
+          <t>454356.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>176809.8</t>
+          <t>191580.74</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>49373.9</v>
+        <v>78358.95</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10661.0</t>
+          <t>12008.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,33 +2712,33 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>96.03</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-76.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>551491.0</t>
+          <t>681031.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>227054.6</t>
+          <t>321219.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>234174.7</t>
+          <t>255754.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>164471.06</t>
+          <t>176809.8</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-7120</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1655.564760526683</t>
+          <t>6195.122263684315</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>18686.23</v>
+        <v>49373.9</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>10661.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-68.02</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-77.68</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>192113.0</t>
+          <t>551491.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>138115.6</t>
+          <t>227054.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>190650.3</t>
+          <t>234174.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>155068.52</t>
+          <t>164471.06</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-52534</t>
+          <t>-7120</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5354.072467350683</t>
+          <t>-1655.564760526683</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-11941.39</v>
+        <v>18686.23</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1057.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-71.34</t>
+          <t>-68.02</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-73.89</t>
+          <t>-77.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>49611.0</t>
+          <t>192113.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>150739.6</t>
+          <t>138115.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>183244.8</t>
+          <t>190650.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>154161.68</t>
+          <t>155068.52</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-32505</t>
+          <t>-52534</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4156.379248009005</t>
+          <t>-5354.072467350683</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-16763.85</v>
+        <v>-11941.39</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2745.0</t>
+          <t>1057.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-17.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>51.09</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-63.27</t>
+          <t>-71.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-73.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>131849.0</t>
+          <t>49611.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>175806.2</t>
+          <t>150739.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>186429.5</t>
+          <t>183244.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>156017.42</t>
+          <t>154161.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-10623</t>
+          <t>-32505</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1864.111113100804</t>
+          <t>-4156.379248009005</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-7786.31</v>
+        <v>-16763.85</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4338.0</t>
+          <t>2745.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.66</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>51.17</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-60.34</t>
+          <t>-63.27</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-64.37</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>210209.0</t>
+          <t>131849.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>190290.2</t>
+          <t>175806.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>178505.4</t>
+          <t>186429.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>154783.0</t>
+          <t>156017.42</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>-10623</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-787.3468324887472</t>
+          <t>-1864.111113100804</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-3494.39</v>
+        <v>-7786.31</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2239.0</t>
+          <t>4338.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.48</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-64.41</t>
+          <t>-60.34</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-58.99</t>
+          <t>-64.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>106796.0</t>
+          <t>210209.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>241294.8</t>
+          <t>190290.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>166253.2</t>
+          <t>178505.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>152073.08</t>
+          <t>154783.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>75041</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-295.1571501936293</t>
+          <t>-787.3468324887472</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-5633.98</v>
+        <v>-3494.39</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5279.0</t>
+          <t>2239.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.49</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-61.80</t>
+          <t>-64.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-58.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76717.33959537571</t>
+          <t>77379.39826839828</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>255233.0</t>
+          <t>106796.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>243185.0</t>
+          <t>241294.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>169332.6</t>
+          <t>166253.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>153829.38</t>
+          <t>152073.08</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>73852</t>
+          <t>75041</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>675.538624081627</t>
+          <t>-295.1571501936293</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>2590.63</v>
+        <v>-5633.98</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>678.2</t>
+          <t>672.05</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>677.46</t>
+          <t>676.22</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3110892215.0</t>
+          <t>3951924444.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2089597881.18</t>
+          <t>2193079344.64</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>272741488.12</v>
+        <v>504555996</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,17 +6201,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6221,37 +6221,37 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>678.2</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>677.46</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>3110892215.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>2089597881.18</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>184622942.89</v>
+        <v>272741488.12</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>681.95</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>677.64</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>2660675287.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>2031062259.28</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>236195769.4</v>
+        <v>184622942.89</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>684.55</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>677.36</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>2688233856.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>2012331643.46</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>194429357.4</v>
+        <v>236195769.4</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>6078.152</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>663.2</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>687.1</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>677.34</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>666.14</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-676.47</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-95.91</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>3950855603.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>2444767042.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>2195634921.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1973519631.2</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>249132120</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>33785075.45068976</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>52995513.02</v>
+        <v>194429357.4</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2587.128</t>
+          <t>3200.569</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-17.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>690.9</t>
+          <t>689.1</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>676.56</t>
+          <t>677.08</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>665.72</t>
+          <t>666.05</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-133.28</t>
+          <t>-219.00</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-88.98</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1720492718.0</t>
+          <t>2125750388.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2044328041.6</t>
+          <t>2117069946.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1858898579.5</t>
+          <t>1936357091.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1901243274.0</t>
+          <t>1916414460.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>185429462</t>
+          <t>180712855</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4226337.417336328</t>
+          <t>4577024.187966792</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>44601454.33</v>
+        <v>52995513.02</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>662.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3583.582</t>
+          <t>2587.128</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.76</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>691.6</t>
+          <t>690.9</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>676.06</t>
+          <t>676.56</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>665.44</t>
+          <t>665.72</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-133.28</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-82.95</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2391568906.0</t>
+          <t>1720492718.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2129942802.4</t>
+          <t>2044328041.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1937240022.2</t>
+          <t>1858898579.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1893640408.06</t>
+          <t>1901243274.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>192702780</t>
+          <t>185429462</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-13104117.73556212</t>
+          <t>-4226337.417336328</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>74437497.48999999</v>
+        <v>44601454.33</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>662.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>664.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2990.66</t>
+          <t>3583.582</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>687.6</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>691.6</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>675.44</t>
+          <t>676.06</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>665.02</t>
+          <t>665.44</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-50.69</t>
+          <t>-86.71</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-72.34</t>
+          <t>-77.27</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2035167596.0</t>
+          <t>2391568906.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2018014894.0</t>
+          <t>2129942802.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1817621011.7</t>
+          <t>1937240022.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1870325126.16</t>
+          <t>1893640408.06</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>200393882</t>
+          <t>192702780</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-29020775.04864686</t>
+          <t>-13104117.73556212</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>42500914.08</v>
+        <v>74437497.48999999</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3424.467</t>
+          <t>2990.66</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-20.96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>693.2</t>
+          <t>687.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>693.5</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>674.24</t>
+          <t>675.44</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>664.54</t>
+          <t>665.02</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-37.33</t>
+          <t>-50.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-68.83</t>
+          <t>-72.34</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2312370123.0</t>
+          <t>2035167596.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1946502801.0</t>
+          <t>2018014894.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1695217335.8</t>
+          <t>1817621011.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1857410869.06</t>
+          <t>1870325126.16</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>251285465</t>
+          <t>200393882</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-42024718.52679587</t>
+          <t>-29020775.04864686</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>33545188.36</v>
+        <v>42500914.08</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>666.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2544.205</t>
+          <t>3424.467</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-20.96</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>693.2</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>693.7</t>
+          <t>693.5</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>673.14</t>
+          <t>674.24</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>664.05</t>
+          <t>664.54</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-21.44</t>
+          <t>-37.33</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-65.92</t>
+          <t>-68.83</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1762040865.0</t>
+          <t>2312370123.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1755644235.8</t>
+          <t>1946502801.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1570290079.0</t>
+          <t>1695217335.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1841151084.92</t>
+          <t>1857410869.06</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>185354156</t>
+          <t>251285465</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-55764701.59648874</t>
+          <t>-42024718.52679587</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-10147018.73</v>
+        <v>33545188.36</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>666.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3097.185</t>
+          <t>2544.205</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,72 +9944,72 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>688.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-22.2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-5.15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-13.28</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-4.15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>7.90</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>714.0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>691.0</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>693.5</t>
+          <t>693.7</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>671.88</t>
+          <t>673.14</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>663.46</t>
+          <t>664.05</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-21.44</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-64.10</t>
+          <t>-65.92</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,45 +10150,45 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>3307081003.025974</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2148566522.0</t>
+          <t>1762040865.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1673469117.4</t>
+          <t>1755644235.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1550878924.7</t>
+          <t>1570290079.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1859076743.5</t>
+          <t>1841151084.92</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>122590192</t>
+          <t>185354156</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-64058825.754549</t>
+          <t>-55764701.59648874</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-13238214.82</v>
+        <v>-10147018.73</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>418174</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>702.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>51.44</t>
+          <t>51.93</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>609252.4</t>
+          <t>516372.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>218290.42</t>
+          <t>220937.42</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>62824.5</v>
+        <v>36551.89</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>648147.4</t>
+          <t>609252.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>212611.62</t>
+          <t>218290.42</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>83071.92999999999</v>
+        <v>62824.5</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,33 +1850,33 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>564572.4</t>
+          <t>648147.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>201223.44</t>
+          <t>212611.62</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>81925.84</v>
+        <v>83071.92999999999</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>454356.8</t>
+          <t>564572.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>191580.74</t>
+          <t>201223.44</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>78358.95</v>
+        <v>81925.84</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,74 +2617,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5.44</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>321219.0</t>
+          <t>454356.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>176809.8</t>
+          <t>191580.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>49373.9</v>
+        <v>78358.95</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10661.0</t>
+          <t>12008.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,33 +3143,33 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>96.03</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-76.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>551491.0</t>
+          <t>681031.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>227054.6</t>
+          <t>321219.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>234174.7</t>
+          <t>255754.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>164471.06</t>
+          <t>176809.8</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-7120</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1655.564760526683</t>
+          <t>6195.122263684315</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>18686.23</v>
+        <v>49373.9</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>10661.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-68.02</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.68</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>192113.0</t>
+          <t>551491.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>138115.6</t>
+          <t>227054.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>190650.3</t>
+          <t>234174.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>155068.52</t>
+          <t>164471.06</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-52534</t>
+          <t>-7120</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5354.072467350683</t>
+          <t>-1655.564760526683</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-11941.39</v>
+        <v>18686.23</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1057.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-71.34</t>
+          <t>-68.02</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-73.89</t>
+          <t>-77.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>49611.0</t>
+          <t>192113.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>150739.6</t>
+          <t>138115.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>183244.8</t>
+          <t>190650.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>154161.68</t>
+          <t>155068.52</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-32505</t>
+          <t>-52534</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4156.379248009005</t>
+          <t>-5354.072467350683</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-16763.85</v>
+        <v>-11941.39</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2745.0</t>
+          <t>1057.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-17.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>51.09</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-63.27</t>
+          <t>-71.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-73.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>131849.0</t>
+          <t>49611.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>175806.2</t>
+          <t>150739.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>186429.5</t>
+          <t>183244.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>156017.42</t>
+          <t>154161.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-10623</t>
+          <t>-32505</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1864.111113100804</t>
+          <t>-4156.379248009005</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-7786.31</v>
+        <v>-16763.85</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4338.0</t>
+          <t>2745.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,37 +4888,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,37 +4928,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.66</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>51.17</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-60.34</t>
+          <t>-63.27</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-64.37</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>210209.0</t>
+          <t>131849.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>190290.2</t>
+          <t>175806.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>178505.4</t>
+          <t>186429.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>154783.0</t>
+          <t>156017.42</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>-10623</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-787.3468324887472</t>
+          <t>-1864.111113100804</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-3494.39</v>
+        <v>-7786.31</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2239.0</t>
+          <t>4338.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.48</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-64.41</t>
+          <t>-60.34</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-58.99</t>
+          <t>-64.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77379.39826839828</t>
+          <t>77736.12536023055</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>106796.0</t>
+          <t>210209.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>241294.8</t>
+          <t>190290.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>166253.2</t>
+          <t>178505.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>152073.08</t>
+          <t>154783.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>75041</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-295.1571501936293</t>
+          <t>-787.3468324887472</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-5633.98</v>
+        <v>-3494.39</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,47 +5547,47 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>7459</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>47.3</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>48.7</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>7622</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>47.1</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>672.05</t>
+          <t>665.8</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>676.22</t>
+          <t>674.84</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3951924444.6</t>
+          <t>3662553443.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2193079344.64</t>
+          <t>2215412102.28</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>504555996</v>
+        <v>367193931.11</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>678.2</t>
+          <t>672.05</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>677.46</t>
+          <t>676.22</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3110892215.0</t>
+          <t>3951924444.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2089597881.18</t>
+          <t>2193079344.64</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>272741488.12</v>
+        <v>504555996</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6652,37 +6652,37 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>678.2</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>677.46</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>3110892215.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>2089597881.18</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>184622942.89</v>
+        <v>272741488.12</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>681.95</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>677.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>2660675287.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>2031062259.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>236195769.4</v>
+        <v>184622942.89</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>684.55</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>677.36</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>2688233856.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>2012331643.46</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>194429357.4</v>
+        <v>236195769.4</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>6078.152</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-17.41</t>
+          <t>-14.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>663.2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>687.1</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>677.34</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>666.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-676.47</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-95.91</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>3950855603.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>2444767042.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>2195634921.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1973519631.2</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>249132120</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>33785075.45068976</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>52995513.02</v>
+        <v>194429357.4</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2587.128</t>
+          <t>3200.569</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-17.76</t>
+          <t>-16.78</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>690.9</t>
+          <t>689.1</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>676.56</t>
+          <t>677.08</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>665.72</t>
+          <t>666.05</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-133.28</t>
+          <t>-219.00</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-88.98</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1720492718.0</t>
+          <t>2125750388.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2044328041.6</t>
+          <t>2117069946.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1858898579.5</t>
+          <t>1936357091.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1901243274.0</t>
+          <t>1916414460.46</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>185429462</t>
+          <t>180712855</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4226337.417336328</t>
+          <t>4577024.187966792</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>44601454.33</v>
+        <v>52995513.02</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>662.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3583.582</t>
+          <t>2587.128</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-17.14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>691.6</t>
+          <t>690.9</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>676.06</t>
+          <t>676.56</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>665.44</t>
+          <t>665.72</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-133.28</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-82.95</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2391568906.0</t>
+          <t>1720492718.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2129942802.4</t>
+          <t>2044328041.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1937240022.2</t>
+          <t>1858898579.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1893640408.06</t>
+          <t>1901243274.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>192702780</t>
+          <t>185429462</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-13104117.73556212</t>
+          <t>-4226337.417336328</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>74437497.48999999</v>
+        <v>44601454.33</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>662.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>664.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2990.66</t>
+          <t>3583.582</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-17.31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>687.6</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>691.6</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>675.44</t>
+          <t>676.06</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>665.02</t>
+          <t>665.44</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-50.69</t>
+          <t>-86.71</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-72.34</t>
+          <t>-77.27</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2035167596.0</t>
+          <t>2391568906.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2018014894.0</t>
+          <t>2129942802.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1817621011.7</t>
+          <t>1937240022.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1870325126.16</t>
+          <t>1893640408.06</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>200393882</t>
+          <t>192702780</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-29020775.04864686</t>
+          <t>-13104117.73556212</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>42500914.08</v>
+        <v>74437497.48999999</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3424.467</t>
+          <t>2990.66</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>693.2</t>
+          <t>687.6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>693.5</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>674.24</t>
+          <t>675.44</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>664.54</t>
+          <t>665.02</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-37.33</t>
+          <t>-50.69</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-68.83</t>
+          <t>-72.34</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2312370123.0</t>
+          <t>2035167596.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1946502801.0</t>
+          <t>2018014894.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1695217335.8</t>
+          <t>1817621011.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1857410869.06</t>
+          <t>1870325126.16</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>251285465</t>
+          <t>200393882</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-42024718.52679587</t>
+          <t>-29020775.04864686</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>33545188.36</v>
+        <v>42500914.08</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>666.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2544.205</t>
+          <t>3424.467</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-22.2</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>693.2</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>693.7</t>
+          <t>693.5</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>673.14</t>
+          <t>674.24</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>664.05</t>
+          <t>664.54</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-21.44</t>
+          <t>-37.33</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-65.92</t>
+          <t>-68.83</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3307081003.025974</t>
+          <t>3307727861.658501</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1762040865.0</t>
+          <t>2312370123.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1755644235.8</t>
+          <t>1946502801.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1570290079.0</t>
+          <t>1695217335.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1841151084.92</t>
+          <t>1857410869.06</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>185354156</t>
+          <t>251285465</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-55764701.59648874</t>
+          <t>-42024718.52679587</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-10147018.73</v>
+        <v>33545188.36</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>418174</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>666.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>51.93</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>516372.6</t>
+          <t>396703.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>220937.42</t>
+          <t>224069.9</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>36551.89</v>
+        <v>15939.42</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>51.44</t>
+          <t>51.93</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>609252.4</t>
+          <t>516372.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>218290.42</t>
+          <t>220937.42</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>62824.5</v>
+        <v>36551.89</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>648147.4</t>
+          <t>609252.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>212611.62</t>
+          <t>218290.42</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>83071.92999999999</v>
+        <v>62824.5</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,33 +2281,33 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>564572.4</t>
+          <t>648147.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>201223.44</t>
+          <t>212611.62</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>81925.84</v>
+        <v>83071.92999999999</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>454356.8</t>
+          <t>564572.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>191580.74</t>
+          <t>201223.44</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>78358.95</v>
+        <v>81925.84</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,74 +3048,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>321219.0</t>
+          <t>454356.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>176809.8</t>
+          <t>191580.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>49373.9</v>
+        <v>78358.95</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10661.0</t>
+          <t>12008.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,22 +3489,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,33 +3574,33 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>96.03</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-76.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>551491.0</t>
+          <t>681031.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>227054.6</t>
+          <t>321219.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>234174.7</t>
+          <t>255754.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>164471.06</t>
+          <t>176809.8</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-7120</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1655.564760526683</t>
+          <t>6195.122263684315</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>18686.23</v>
+        <v>49373.9</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>10661.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-68.02</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-77.68</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>192113.0</t>
+          <t>551491.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>138115.6</t>
+          <t>227054.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>190650.3</t>
+          <t>234174.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>155068.52</t>
+          <t>164471.06</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-52534</t>
+          <t>-7120</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5354.072467350683</t>
+          <t>-1655.564760526683</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-11941.39</v>
+        <v>18686.23</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1057.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-71.34</t>
+          <t>-68.02</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-73.89</t>
+          <t>-77.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>49611.0</t>
+          <t>192113.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>150739.6</t>
+          <t>138115.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>183244.8</t>
+          <t>190650.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>154161.68</t>
+          <t>155068.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-32505</t>
+          <t>-52534</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4156.379248009005</t>
+          <t>-5354.072467350683</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-16763.85</v>
+        <v>-11941.39</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,47 +4685,47 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
+          <t>48.69</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>7409</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>48.2</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>7459</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>47.55</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>46.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2745.0</t>
+          <t>1057.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-17.74</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>51.09</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-63.27</t>
+          <t>-71.34</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-73.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>131849.0</t>
+          <t>49611.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>175806.2</t>
+          <t>150739.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>186429.5</t>
+          <t>183244.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>156017.42</t>
+          <t>154161.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-10623</t>
+          <t>-32505</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1864.111113100804</t>
+          <t>-4156.379248009005</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-7786.31</v>
+        <v>-16763.85</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4338.0</t>
+          <t>2745.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>19.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5319,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,37 +5359,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.66</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>51.17</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-60.34</t>
+          <t>-63.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-64.37</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77736.12536023055</t>
+          <t>78054.18992805755</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>210209.0</t>
+          <t>131849.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>190290.2</t>
+          <t>175806.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>178505.4</t>
+          <t>186429.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>154783.0</t>
+          <t>156017.42</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>-10623</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-787.3468324887472</t>
+          <t>-1864.111113100804</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-3494.39</v>
+        <v>-7786.31</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,210 +5750,210 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>659.5</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>673.4</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>3307526656.607913</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>3434438489.8</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>2234436035.54</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>232455110.29</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>3307727861.658501</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>367193931.11</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>672.05</t>
+          <t>665.8</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>676.22</t>
+          <t>674.84</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3951924444.6</t>
+          <t>3662553443.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2193079344.64</t>
+          <t>2215412102.28</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>504555996</v>
+        <v>367193931.11</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>678.2</t>
+          <t>672.05</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>677.46</t>
+          <t>676.22</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3110892215.0</t>
+          <t>3951924444.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2089597881.18</t>
+          <t>2193079344.64</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>272741488.12</v>
+        <v>504555996</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,17 +7063,17 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7083,37 +7083,37 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>678.2</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>677.46</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>3110892215.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>2089597881.18</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>184622942.89</v>
+        <v>272741488.12</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>681.95</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>677.64</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>2660675287.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>2031062259.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>236195769.4</v>
+        <v>184622942.89</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>684.55</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>677.36</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>2688233856.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>2012331643.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>194429357.4</v>
+        <v>236195769.4</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>6078.152</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-16.78</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>663.2</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>687.1</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>677.34</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>666.14</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-676.47</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-95.91</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>3950855603.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>2444767042.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>2195634921.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1973519631.2</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>249132120</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>33785075.45068976</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>52995513.02</v>
+        <v>194429357.4</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2587.128</t>
+          <t>3200.569</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-17.14</t>
+          <t>-15.36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>690.9</t>
+          <t>689.1</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>676.56</t>
+          <t>677.08</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>665.72</t>
+          <t>666.05</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-133.28</t>
+          <t>-219.00</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-88.98</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1720492718.0</t>
+          <t>2125750388.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2044328041.6</t>
+          <t>2117069946.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1858898579.5</t>
+          <t>1936357091.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1901243274.0</t>
+          <t>1916414460.46</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>185429462</t>
+          <t>180712855</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4226337.417336328</t>
+          <t>4577024.187966792</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>44601454.33</v>
+        <v>52995513.02</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>662.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3583.582</t>
+          <t>2587.128</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-17.31</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>691.6</t>
+          <t>690.9</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>676.06</t>
+          <t>676.56</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>665.44</t>
+          <t>665.72</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-133.28</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-82.95</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2391568906.0</t>
+          <t>1720492718.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2129942802.4</t>
+          <t>2044328041.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1937240022.2</t>
+          <t>1858898579.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1893640408.06</t>
+          <t>1901243274.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>192702780</t>
+          <t>185429462</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-13104117.73556212</t>
+          <t>-4226337.417336328</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>74437497.48999999</v>
+        <v>44601454.33</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>662.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>664.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2990.66</t>
+          <t>3583.582</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>687.6</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>691.6</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>675.44</t>
+          <t>676.06</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>665.02</t>
+          <t>665.44</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-50.69</t>
+          <t>-86.71</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-72.34</t>
+          <t>-77.27</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2035167596.0</t>
+          <t>2391568906.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2018014894.0</t>
+          <t>2129942802.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1817621011.7</t>
+          <t>1937240022.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1870325126.16</t>
+          <t>1893640408.06</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>200393882</t>
+          <t>192702780</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-29020775.04864686</t>
+          <t>-13104117.73556212</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>42500914.08</v>
+        <v>74437497.48999999</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>678.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3424.467</t>
+          <t>2990.66</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>693.2</t>
+          <t>687.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>693.5</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>674.24</t>
+          <t>675.44</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>664.54</t>
+          <t>665.02</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-37.33</t>
+          <t>-50.69</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-68.83</t>
+          <t>-72.34</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3307727861.658501</t>
+          <t>3307526656.607913</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2312370123.0</t>
+          <t>2035167596.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1946502801.0</t>
+          <t>2018014894.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1695217335.8</t>
+          <t>1817621011.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1857410869.06</t>
+          <t>1870325126.16</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>251285465</t>
+          <t>200393882</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-42024718.52679587</t>
+          <t>-29020775.04864686</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>33545188.36</v>
+        <v>42500914.08</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>425601</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,17 +10313,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>666.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,50 +1104,50 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>336883.6</t>
+          <t>259217.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>229641.16</t>
+          <t>233052.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>301588</v>
+        <v>221658</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>396703.8</t>
+          <t>336883.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>224069.9</t>
+          <t>229641.16</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>199194</v>
+        <v>301588</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>51.93</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,50 +1976,50 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>516372.6</t>
+          <t>396703.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>220937.42</t>
+          <t>224069.9</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>216632</v>
+        <v>199194</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>51.44</t>
+          <t>51.93</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,50 +2412,50 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>609252.4</t>
+          <t>516372.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>218290.42</t>
+          <t>220937.42</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>357016</v>
+        <v>216632</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2520,17 +2520,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-18.08</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,50 +2848,50 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>648147.4</t>
+          <t>609252.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>212611.62</t>
+          <t>218290.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>83071.93395825941</t>
+          <t>62824.50483930594</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>609988</v>
+        <v>357016</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,33 +3173,33 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,50 +3284,50 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>564572.4</t>
+          <t>648147.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>201223.44</t>
+          <t>212611.62</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>81925.83505825518</t>
+          <t>83071.93395825941</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>600689</v>
+        <v>609988</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-13.56</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>454356.8</t>
+          <t>564572.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>191580.74</t>
+          <t>201223.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>78358.94966331136</t>
+          <t>81925.83505825518</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>797538</v>
+        <v>600689</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,74 +3950,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-12.29</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-8.1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,50 +4156,50 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>321219.0</t>
+          <t>454356.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>176809.8</t>
+          <t>191580.74</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>49373.9008968448</t>
+          <t>78358.94966331136</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>681031</v>
+        <v>797538</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10661.0</t>
+          <t>12008.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,22 +4396,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,33 +4481,33 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>96.03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-76.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,50 +4592,50 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>551491.0</t>
+          <t>681031.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>227054.6</t>
+          <t>321219.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>234174.7</t>
+          <t>255754.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>164471.06</t>
+          <t>176809.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-7120</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1655.564760526683</t>
+          <t>6195.122263684315</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>18686.22762700531</t>
+          <t>49373.9008968448</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>551491</v>
+        <v>681031</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>10661.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-68.02</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.68</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>192113.0</t>
+          <t>551491.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>138115.6</t>
+          <t>227054.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>190650.3</t>
+          <t>234174.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>155068.52</t>
+          <t>164471.06</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-52534</t>
+          <t>-7120</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5354.072467350683</t>
+          <t>-1655.564760526683</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11941.38517372991</t>
+          <t>18686.22762700531</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>192113</v>
+        <v>551491</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1057.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-71.34</t>
+          <t>-68.02</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-73.89</t>
+          <t>-77.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>78592.0172413793</t>
+          <t>78956.28550932568</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>49611.0</t>
+          <t>192113.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>150739.6</t>
+          <t>138115.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>183244.8</t>
+          <t>190650.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>154161.68</t>
+          <t>155068.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-32505</t>
+          <t>-52534</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4156.379248009005</t>
+          <t>-5354.072467350683</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-16763.85399000411</t>
+          <t>-11941.38517372991</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>49611</v>
+        <v>192113</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7309.42</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>585.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5705.448</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>573.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>653.25</t>
+          <t>646.8</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>671.96</t>
+          <t>670.44</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3639148367.2</t>
+          <t>3701315712.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2279747515.3</t>
+          <t>2315429027.54</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>3277325446</v>
+        <v>4282414081</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>653.25</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>673.4</t>
+          <t>671.96</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3434438489.8</t>
+          <t>3639148367.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2234436035.54</t>
+          <t>2279747515.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>2111926901</v>
+        <v>3277325446</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,215 +6682,215 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>659.5</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>673.4</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>3314305072.644189</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>3434438489.8</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>2234436035.54</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>2111926901</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>3309837664.528017</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>2504000596</v>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>672.05</t>
+          <t>665.8</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>676.22</t>
+          <t>674.84</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3951924444.6</t>
+          <t>3662553443.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2193079344.64</t>
+          <t>2215412102.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>6330911536</v>
+        <v>2504000596</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>678.2</t>
+          <t>672.05</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>677.46</t>
+          <t>676.22</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3110892215.0</t>
+          <t>3951924444.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2089597881.18</t>
+          <t>2193079344.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>272741488.1174035</t>
+          <t>504555995.9956522</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>3971577357</v>
+        <v>6330911536</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -8030,37 +8030,37 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>678.2</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>677.46</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>3110892215.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>2089597881.18</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>184622942.8942842</t>
+          <t>272741488.1174035</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>2253776059</v>
+        <v>3971577357</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>681.95</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>677.64</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>2660675287.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>2031062259.28</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>236195769.4007463</t>
+          <t>184622942.8942842</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>3252501668</v>
+        <v>2253776059</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8619,12 +8619,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,17 +8684,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>684.55</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>677.36</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>2688233856.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>2012331643.46</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>194429357.3956661</t>
+          <t>236195769.4007463</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>3950855603</v>
+        <v>3252501668</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>6078.152</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-15.36</t>
+          <t>-10.6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>663.2</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>687.1</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>677.34</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>666.14</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-676.47</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-95.91</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>3950855603.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>2444767042.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>2195634921.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1973519631.2</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>249132120</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>33785075.45068976</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>52995513.01713395</t>
+          <t>194429357.3956661</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>2125750388</v>
+        <v>3950855603</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2587.128</t>
+          <t>3200.569</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>690.9</t>
+          <t>689.1</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>676.56</t>
+          <t>677.08</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>665.72</t>
+          <t>666.05</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-133.28</t>
+          <t>-219.00</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-88.98</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1720492718.0</t>
+          <t>2125750388.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2044328041.6</t>
+          <t>2117069946.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1858898579.5</t>
+          <t>1936357091.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1901243274.0</t>
+          <t>1916414460.46</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>185429462</t>
+          <t>180712855</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4226337.417336328</t>
+          <t>4577024.187966792</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>44601454.33290553</t>
+          <t>52995513.01713395</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1720492718</v>
+        <v>2125750388</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>662.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3583.582</t>
+          <t>2587.128</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>691.6</t>
+          <t>690.9</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>676.06</t>
+          <t>676.56</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>665.44</t>
+          <t>665.72</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-133.28</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-82.95</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3309837664.528017</t>
+          <t>3314305072.644189</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2391568906.0</t>
+          <t>1720492718.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2129942802.4</t>
+          <t>2044328041.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1937240022.2</t>
+          <t>1858898579.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1893640408.06</t>
+          <t>1901243274.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>192702780</t>
+          <t>185429462</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-13104117.73556212</t>
+          <t>-4226337.417336328</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>74437497.48640394</t>
+          <t>44601454.33290553</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2391568906</v>
+        <v>1720492718</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>425601</t>
+          <t>434515</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
+          <t>662.0</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>663.0</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>664.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4120.0</t>
+          <t>3922.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,72 +898,72 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-44.99</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-42.86</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.18000000000001</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-31.48</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,50 +1104,50 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>259217.6</t>
+          <t>231160.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>453682.5</t>
+          <t>420206.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>233052.36</t>
+          <t>235339.22</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-194464</t>
+          <t>-189045</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>26429.75007447299</t>
+          <t>20734.78860529711</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2426.165298745036</t>
+          <t>-10587.49947517022</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>221658</v>
+        <v>216732</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>336883.6</t>
+          <t>259217.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>229641.16</t>
+          <t>233052.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>301588</v>
+        <v>221658</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>396703.8</t>
+          <t>336883.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>224069.9</t>
+          <t>229641.16</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>199194</v>
+        <v>301588</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>51.93</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>516372.6</t>
+          <t>396703.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>220937.42</t>
+          <t>224069.9</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>216632</v>
+        <v>199194</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>51.44</t>
+          <t>51.93</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>609252.4</t>
+          <t>516372.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>218290.42</t>
+          <t>220937.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>357016</v>
+        <v>216632</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>648147.4</t>
+          <t>609252.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>212611.62</t>
+          <t>218290.42</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>83071.93395825941</t>
+          <t>62824.50483930594</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>609988</v>
+        <v>357016</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-14.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,33 +3609,33 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>564572.4</t>
+          <t>648147.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>201223.44</t>
+          <t>212611.62</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>81925.83505825518</t>
+          <t>83071.93395825941</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>600689</v>
+        <v>609988</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>454356.8</t>
+          <t>564572.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>191580.74</t>
+          <t>201223.44</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>78358.94966331136</t>
+          <t>81925.83505825518</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>797538</v>
+        <v>600689</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,74 +4386,74 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-9.64</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-6.89</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>321219.0</t>
+          <t>454356.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>176809.8</t>
+          <t>191580.74</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>49373.9008968448</t>
+          <t>78358.94966331136</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>681031</v>
+        <v>797538</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10661.0</t>
+          <t>12008.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,22 +4832,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,33 +4917,33 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>96.03</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-76.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,50 +5028,50 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>551491.0</t>
+          <t>681031.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>227054.6</t>
+          <t>321219.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>234174.7</t>
+          <t>255754.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>164471.06</t>
+          <t>176809.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-7120</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1655.564760526683</t>
+          <t>6195.122263684315</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>18686.22762700531</t>
+          <t>49373.9008968448</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>551491</v>
+        <v>681031</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>10661.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-68.02</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-77.68</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>78956.28550932568</t>
+          <t>79308.92406876791</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>192113.0</t>
+          <t>551491.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>138115.6</t>
+          <t>227054.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>190650.3</t>
+          <t>234174.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>155068.52</t>
+          <t>164471.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-52534</t>
+          <t>-7120</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5354.072467350683</t>
+          <t>-1655.564760526683</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-11941.38517372991</t>
+          <t>18686.22762700531</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>192113</v>
+        <v>551491</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7309.42</t>
+          <t>3906.167</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>-15.42</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.34</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>572.0</t>
+          <t>577.4</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>646.8</t>
+          <t>640.85</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>670.44</t>
+          <t>668.88</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>660.9</t>
+          <t>660.11</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-32.16</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-29.38</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-19.98</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-186.14</t>
+          <t>-193.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3701315712.0</t>
+          <t>2895931468.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3406103963.5</t>
+          <t>3423927956.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2315429027.54</t>
+          <t>2313304958.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>295211748</t>
+          <t>-527996488</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>220199973.5705063</t>
+          <t>212169345.7292535</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>280713247.2140913</t>
+          <t>168000892.6023631</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>4282414081</v>
+        <v>2303990317</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>580.0</t>
+          <t>589.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>593.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5705.448</t>
+          <t>7309.42</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>653.25</t>
+          <t>646.8</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>671.96</t>
+          <t>670.44</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3639148367.2</t>
+          <t>3701315712.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2279747515.3</t>
+          <t>2315429027.54</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>3277325446</v>
+        <v>4282414081</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>653.25</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>673.4</t>
+          <t>671.96</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3434438489.8</t>
+          <t>3639148367.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2234436035.54</t>
+          <t>2279747515.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>2111926901</v>
+        <v>3277325446</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,215 +7118,215 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>659.5</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>673.4</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>3314508053.16404</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>3434438489.8</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>2234436035.54</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>2111926901</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>3314305072.644189</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD16" t="n">
-        <v>2504000596</v>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>672.05</t>
+          <t>665.8</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>676.22</t>
+          <t>674.84</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3951924444.6</t>
+          <t>3662553443.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2193079344.64</t>
+          <t>2215412102.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>6330911536</v>
+        <v>2504000596</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>678.2</t>
+          <t>672.05</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>677.46</t>
+          <t>676.22</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3110892215.0</t>
+          <t>3951924444.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2089597881.18</t>
+          <t>2193079344.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>272741488.1174035</t>
+          <t>504555995.9956522</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>3971577357</v>
+        <v>6330911536</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,17 +8446,17 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -8466,37 +8466,37 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>678.2</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>677.46</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>3110892215.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>2089597881.18</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>184622942.8942842</t>
+          <t>272741488.1174035</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>2253776059</v>
+        <v>3971577357</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>681.95</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>677.64</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>2660675287.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>2031062259.28</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>236195769.4007463</t>
+          <t>184622942.8942842</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>3252501668</v>
+        <v>2253776059</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9055,12 +9055,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.6</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>684.55</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>677.36</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>2688233856.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>2012331643.46</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>194429357.3956661</t>
+          <t>236195769.4007463</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>3950855603</v>
+        <v>3252501668</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9496,17 +9496,17 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>6078.152</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-9.66</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>663.2</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>687.1</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>677.34</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>666.14</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-676.47</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-95.91</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>3950855603.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>2444767042.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>2195634921.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1973519631.2</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>249132120</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>33785075.45068976</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>52995513.01713395</t>
+          <t>194429357.3956661</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>2125750388</v>
+        <v>3950855603</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2587.128</t>
+          <t>3200.569</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>690.9</t>
+          <t>689.1</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>676.56</t>
+          <t>677.08</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>665.72</t>
+          <t>666.05</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-133.28</t>
+          <t>-219.00</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-88.98</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3314305072.644189</t>
+          <t>3314508053.16404</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1720492718.0</t>
+          <t>2125750388.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2044328041.6</t>
+          <t>2117069946.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1858898579.5</t>
+          <t>1936357091.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1901243274.0</t>
+          <t>1916414460.46</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>185429462</t>
+          <t>180712855</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4226337.417336328</t>
+          <t>4577024.187966792</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>44601454.33290553</t>
+          <t>52995513.01713395</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>1720492718</v>
+        <v>2125750388</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>662.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>661.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3922.0</t>
+          <t>2793.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-44.99</t>
+          <t>-40.68</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.41</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-36.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>231160.8</t>
+          <t>217717.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>420206.6</t>
+          <t>367044.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>235339.22</t>
+          <t>237158.66</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-189045</t>
+          <t>-149327</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>20734.78860529711</t>
+          <t>14301.02560266853</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10587.49947517022</t>
+          <t>-21084.67091178865</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>216732</v>
+        <v>149413</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4120.0</t>
+          <t>3922.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,72 +1334,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-4.76</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-44.99</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-42.86</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.18000000000001</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-31.48</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>259217.6</t>
+          <t>231160.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>453682.5</t>
+          <t>420206.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>233052.36</t>
+          <t>235339.22</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-194464</t>
+          <t>-189045</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>26429.75007447299</t>
+          <t>20734.78860529711</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2426.165298745036</t>
+          <t>-10587.49947517022</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>221658</v>
+        <v>216732</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>336883.6</t>
+          <t>259217.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>229641.16</t>
+          <t>233052.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>301588</v>
+        <v>221658</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>396703.8</t>
+          <t>336883.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>224069.9</t>
+          <t>229641.16</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>199194</v>
+        <v>301588</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-12.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>51.93</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>516372.6</t>
+          <t>396703.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>220937.42</t>
+          <t>224069.9</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>216632</v>
+        <v>199194</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>51.44</t>
+          <t>51.93</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>609252.4</t>
+          <t>516372.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>218290.42</t>
+          <t>220937.42</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>357016</v>
+        <v>216632</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>648147.4</t>
+          <t>609252.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>212611.62</t>
+          <t>218290.42</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>83071.93395825941</t>
+          <t>62824.50483930594</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>609988</v>
+        <v>357016</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-19.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,33 +4045,33 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>564572.4</t>
+          <t>648147.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>201223.44</t>
+          <t>212611.62</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>81925.83505825518</t>
+          <t>83071.93395825941</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>600689</v>
+        <v>609988</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>454356.8</t>
+          <t>564572.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>191580.74</t>
+          <t>201223.44</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>78358.94966331136</t>
+          <t>81925.83505825518</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>797538</v>
+        <v>600689</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,74 +4822,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-4.36</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>321219.0</t>
+          <t>454356.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>176809.8</t>
+          <t>191580.74</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>49373.9008968448</t>
+          <t>78358.94966331136</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>681031</v>
+        <v>797538</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10661.0</t>
+          <t>12008.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,22 +5268,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,33 +5353,33 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>96.03</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-76.31</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,50 +5464,50 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79308.92406876791</t>
+          <t>79516.09227467811</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>551491.0</t>
+          <t>681031.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>227054.6</t>
+          <t>321219.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>234174.7</t>
+          <t>255754.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>164471.06</t>
+          <t>176809.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-7120</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1655.564760526683</t>
+          <t>6195.122263684315</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>18686.22762700531</t>
+          <t>49373.9008968448</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>551491</v>
+        <v>681031</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3906.167</t>
+          <t>3697.739</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.42</t>
+          <t>-12.55</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>44.92</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>586.6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>640.85</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>668.88</t>
+          <t>667.3</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>660.11</t>
+          <t>659.49</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-32.16</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-193.67</t>
+          <t>-197.45</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2895931468.2</t>
+          <t>2845492684.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3423927956.4</t>
+          <t>3254023064.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2313304958.2</t>
+          <t>2250939639.92</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-527996488</t>
+          <t>-408530379</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>212169345.7292535</t>
+          <t>191987669.3415367</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>168000892.6023631</t>
+          <t>80988449.20909452</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>2303990317</v>
+        <v>2251806679</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>594.0</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>584.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7309.42</t>
+          <t>3906.167</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>-15.42</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.34</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>572.0</t>
+          <t>577.4</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>646.8</t>
+          <t>640.85</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>670.44</t>
+          <t>668.88</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>660.9</t>
+          <t>660.11</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-32.16</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-29.38</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-19.98</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-186.14</t>
+          <t>-193.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3701315712.0</t>
+          <t>2895931468.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3406103963.5</t>
+          <t>3423927956.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2315429027.54</t>
+          <t>2313304958.2</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>295211748</t>
+          <t>-527996488</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>220199973.5705063</t>
+          <t>212169345.7292535</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>280713247.2140913</t>
+          <t>168000892.6023631</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>4282414081</v>
+        <v>2303990317</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>580.0</t>
+          <t>589.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>593.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5705.448</t>
+          <t>7309.42</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>653.25</t>
+          <t>646.8</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>671.96</t>
+          <t>670.44</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3639148367.2</t>
+          <t>3701315712.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2279747515.3</t>
+          <t>2315429027.54</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>3277325446</v>
+        <v>4282414081</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>653.25</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>673.4</t>
+          <t>671.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3434438489.8</t>
+          <t>3639148367.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2234436035.54</t>
+          <t>2279747515.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>2111926901</v>
+        <v>3277325446</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,215 +7554,215 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>659.5</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>673.4</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>3314598470.854077</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>3434438489.8</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>2234436035.54</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>2111926901</v>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>3314508053.16404</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD17" t="n">
-        <v>2504000596</v>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>672.05</t>
+          <t>665.8</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>676.22</t>
+          <t>674.84</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3951924444.6</t>
+          <t>3662553443.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2193079344.64</t>
+          <t>2215412102.28</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>6330911536</v>
+        <v>2504000596</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>678.2</t>
+          <t>672.05</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>677.46</t>
+          <t>676.22</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3110892215.0</t>
+          <t>3951924444.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2089597881.18</t>
+          <t>2193079344.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>272741488.1174035</t>
+          <t>504555995.9956522</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>3971577357</v>
+        <v>6330911536</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,17 +8882,17 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8902,37 +8902,37 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>678.2</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>677.46</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>3110892215.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>2089597881.18</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>184622942.8942842</t>
+          <t>272741488.1174035</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>2253776059</v>
+        <v>3971577357</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>681.95</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>677.64</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>2660675287.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>2031062259.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>236195769.4007463</t>
+          <t>184622942.8942842</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>3252501668</v>
+        <v>2253776059</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.66</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>684.55</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>677.36</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>2688233856.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>2012331643.46</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>194429357.3956661</t>
+          <t>236195769.4007463</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>3950855603</v>
+        <v>3252501668</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>6078.152</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>663.2</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>687.1</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>677.34</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>666.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-676.47</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-95.91</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3314508053.16404</t>
+          <t>3314598470.854077</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>3950855603.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>2444767042.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>2195634921.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1973519631.2</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>249132120</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>33785075.45068976</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>52995513.01713395</t>
+          <t>194429357.3956661</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2125750388</v>
+        <v>3950855603</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>438228</t>
+          <t>454569</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>217717</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>149413</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>216732</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>221658</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>301588</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>199194</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>216632</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>357016</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>609988</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>600689</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>797538</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>321219</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>681031</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2251806679</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2303990317</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>4282414081</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3277325446</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2111926901</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2504000596</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>6330911536</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>3971577357</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2253776059</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>3252501668</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3950855603</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2793.0</t>
+          <t>2660.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-40.68</t>
+          <t>-31.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>53.82000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>53.32</v>
+        <v>53.79</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.41</v>
+        <v>49.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-36.99</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>217717</v>
+        <v>206856.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>367044.8</t>
+          <t>301780.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>237158.66</v>
+        <v>239526.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-149327</t>
+          <t>-94923</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>14301.02560266853</t>
+          <t>7755.548718469247</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-21084.67091178865</t>
+          <t>-28244.57414462682</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3922.0</t>
+          <t>2793.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-44.99</t>
+          <t>-40.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.92</v>
+        <v>53.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.09</v>
+        <v>49.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-36.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>231160.8</v>
+        <v>217717</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>420206.6</t>
+          <t>367044.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>235339.22</v>
+        <v>237158.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-189045</t>
+          <t>-149327</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20734.78860529711</t>
+          <t>14301.02560266853</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10587.49947517022</t>
+          <t>-21084.67091178865</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4120.0</t>
+          <t>3922.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,74 +1758,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-44.99</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-42.86</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.18000000000001</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.64</v>
+        <v>52.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>48.75</v>
+        <v>49.09</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-31.48</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>259217.6</v>
+        <v>231160.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>453682.5</t>
+          <t>420206.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>233052.36</v>
+        <v>235339.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-194464</t>
+          <t>-189045</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>26429.75007447299</t>
+          <t>20734.78860529711</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2426.165298745036</t>
+          <t>-10587.49947517022</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.53</v>
+        <v>52.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.48</v>
+        <v>48.75</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>336883.6</v>
+        <v>259217.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>229641.16</v>
+        <v>233052.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-12.38</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.4</v>
+        <v>52.53</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.2</v>
+        <v>48.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>396703.8</v>
+        <v>336883.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>224069.9</v>
+        <v>229641.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-13.14</t>
+          <t>-7.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>51.93</v>
+        <v>52.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>516372.6</v>
+        <v>396703.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>220937.42</v>
+        <v>224069.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>51.44</v>
+        <v>51.93</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>609252.4</v>
+        <v>516372.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>218290.42</v>
+        <v>220937.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-19.43</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50.92</v>
+        <v>51.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.95</v>
+        <v>47.4</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>648147.4</v>
+        <v>609252.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>212611.62</v>
+        <v>218290.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>83071.93395825941</t>
+          <t>62824.50483930594</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-14.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,33 +4433,33 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.29</v>
+        <v>50.92</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.43</v>
+        <v>46.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>564572.4</v>
+        <v>648147.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>201223.44</v>
+        <v>212611.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>81925.83505825518</t>
+          <t>83071.93395825941</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.91</v>
+        <v>50.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.95</v>
+        <v>46.43</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>454356.8</v>
+        <v>564572.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>191580.74</v>
+        <v>201223.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>78358.94966331136</t>
+          <t>81925.83505825518</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12008.0</t>
+          <t>13309.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,74 +5198,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-10.04</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>44.20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-9.33</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>96.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.55</v>
+        <v>49.91</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.52</v>
+        <v>45.95</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.31</t>
+          <t>-70.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79516.09227467811</t>
+          <t>79712.98285714285</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>321219</v>
+        <v>454356.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>255754.6</t>
+          <t>315081.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>176809.8</v>
+        <v>191580.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6195.122263684315</t>
+          <t>17297.24955593463</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>49373.9008968448</t>
+          <t>78358.94966331136</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>681031.0</t>
+          <t>797538.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3697.739</t>
+          <t>2851.548</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.55</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.96</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>586.6</t>
+          <t>594.2</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>636</v>
+        <v>631.1</v>
       </c>
       <c r="AN13" t="n">
-        <v>667.3</v>
+        <v>665.38</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>659.49</t>
+          <t>658.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-22.86</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-197.45</t>
+          <t>-198.54</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>2845492684.8</v>
+        <v>2772989177.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3254023064.0</t>
+          <t>3103713833.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>2250939639.92</v>
+        <v>2209332488.54</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-408530379</t>
+          <t>-330724656</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>191987669.3415367</t>
+          <t>159431909.2972355</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>80988449.20909452</t>
+          <t>-19624770.94642115</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3906.167</t>
+          <t>3697.739</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.42</t>
+          <t>-12.55</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>44.92</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>586.6</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>640.85</v>
+        <v>636</v>
       </c>
       <c r="AN14" t="n">
-        <v>668.88</v>
+        <v>667.3</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>660.11</t>
+          <t>659.49</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-32.16</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-193.67</t>
+          <t>-197.45</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2895931468.2</v>
+        <v>2845492684.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3423927956.4</t>
+          <t>3254023064.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>2313304958.2</v>
+        <v>2250939639.92</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-527996488</t>
+          <t>-408530379</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>212169345.7292535</t>
+          <t>191987669.3415367</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>168000892.6023631</t>
+          <t>80988449.20909452</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>594.0</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>584.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7309.42</t>
+          <t>3906.167</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>-15.42</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.34</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>572.0</t>
+          <t>577.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>646.8</v>
+        <v>640.85</v>
       </c>
       <c r="AN15" t="n">
-        <v>670.4400000000001</v>
+        <v>668.88</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>660.9</t>
+          <t>660.11</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-32.16</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-29.38</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-19.98</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-186.14</t>
+          <t>-193.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3701315712</v>
+        <v>2895931468.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3406103963.5</t>
+          <t>3423927956.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>2315429027.54</v>
+        <v>2313304958.2</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>295211748</t>
+          <t>-527996488</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>220199973.5705063</t>
+          <t>212169345.7292535</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>280713247.2140913</t>
+          <t>168000892.6023631</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>580.0</t>
+          <t>589.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>593.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5705.448</t>
+          <t>7309.42</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>653.25</v>
+        <v>646.8</v>
       </c>
       <c r="AN16" t="n">
-        <v>671.96</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3639148367.2</v>
+        <v>3701315712</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>2279747515.3</v>
+        <v>2315429027.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>659.5</v>
+        <v>653.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>673.4</v>
+        <v>671.96</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3434438489.8</v>
+        <v>3639148367.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>2234436035.54</v>
+        <v>2279747515.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,206 +7894,206 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>673.4</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>3313612064.535</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>3434438489.8</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2234436035.54</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>665.8</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>674.84</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>3314598470.854077</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>3662553443.2</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2215412102.28</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT18" t="inlineStr">
         <is>
           <t>5.56</t>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>672.05</v>
+        <v>665.8</v>
       </c>
       <c r="AN19" t="n">
-        <v>676.22</v>
+        <v>674.84</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3951924444.6</v>
+        <v>3662553443.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>2193079344.64</v>
+        <v>2215412102.28</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>678.2</v>
+        <v>672.05</v>
       </c>
       <c r="AN20" t="n">
-        <v>677.46</v>
+        <v>676.22</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3110892215</v>
+        <v>3951924444.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>2089597881.18</v>
+        <v>2193079344.64</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>272741488.1174035</t>
+          <t>504555995.9956522</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,17 +9204,17 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9224,33 +9224,33 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>681.95</v>
+        <v>678.2</v>
       </c>
       <c r="AN21" t="n">
-        <v>677.64</v>
+        <v>677.46</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>2660675287.2</v>
+        <v>3110892215</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2031062259.28</v>
+        <v>2089597881.18</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>184622942.8942842</t>
+          <t>272741488.1174035</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>684.55</v>
+        <v>681.95</v>
       </c>
       <c r="AN22" t="n">
-        <v>677.36</v>
+        <v>677.64</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>2688233856.6</v>
+        <v>2660675287.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2012331643.46</v>
+        <v>2031062259.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>236195769.4007463</t>
+          <t>184622942.8942842</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>5110.97</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>653.6</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>687.1</v>
+        <v>684.55</v>
       </c>
       <c r="AN23" t="n">
-        <v>677.34</v>
+        <v>677.36</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>666.06</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-809.67</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3314598470.854077</t>
+          <t>3313612064.535</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>2444767042.2</v>
+        <v>2688233856.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>2353124375.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1973519631.2</v>
+        <v>2012331643.46</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>335109481</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>64925182.21223693</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>194429357.3956661</t>
+          <t>236195769.4007463</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>3252501668.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>454569</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>648.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>649.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>633.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2660.0</t>
+          <t>1771.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-33.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>53.82000000000001</t>
+          <t>54.12</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>53.79</v>
+        <v>54.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.76</v>
+        <v>50.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-27.89</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-44.62</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>206856.8</v>
+        <v>166065.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>301780.3</t>
+          <t>251474.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>239526.02</v>
+        <v>241154.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-94923</t>
+          <t>-85408</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7755.548718469247</t>
+          <t>1009.327061166613</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-28244.57414462682</t>
+          <t>-36094.89205399787</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2793.0</t>
+          <t>2660.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-40.68</t>
+          <t>-31.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>53.82000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.32</v>
+        <v>53.79</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.41</v>
+        <v>49.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-36.99</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>217717</v>
+        <v>206856.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>367044.8</t>
+          <t>301780.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>237158.66</v>
+        <v>239526.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-149327</t>
+          <t>-94923</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>14301.02560266853</t>
+          <t>7755.548718469247</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-21084.67091178865</t>
+          <t>-28244.57414462682</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3922.0</t>
+          <t>2793.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-44.99</t>
+          <t>-40.68</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.92</v>
+        <v>53.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.09</v>
+        <v>49.41</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-36.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>231160.8</v>
+        <v>217717</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>420206.6</t>
+          <t>367044.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>235339.22</v>
+        <v>237158.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-189045</t>
+          <t>-149327</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20734.78860529711</t>
+          <t>14301.02560266853</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10587.49947517022</t>
+          <t>-21084.67091178865</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4120.0</t>
+          <t>3922.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,74 +2188,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-44.99</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-42.86</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>40.25</t>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.18000000000001</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.64</v>
+        <v>52.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.75</v>
+        <v>49.09</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-31.48</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>259217.6</v>
+        <v>231160.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>453682.5</t>
+          <t>420206.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>233052.36</v>
+        <v>235339.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-194464</t>
+          <t>-189045</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>26429.75007447299</t>
+          <t>20734.78860529711</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2426.165298745036</t>
+          <t>-10587.49947517022</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.53</v>
+        <v>52.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.48</v>
+        <v>48.75</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>336883.6</v>
+        <v>259217.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>229641.16</v>
+        <v>233052.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.4</v>
+        <v>52.53</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.2</v>
+        <v>48.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>396703.8</v>
+        <v>336883.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>224069.9</v>
+        <v>229641.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>51.93</v>
+        <v>52.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>516372.6</v>
+        <v>396703.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>220937.42</v>
+        <v>224069.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>51.44</v>
+        <v>51.93</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>609252.4</v>
+        <v>516372.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>218290.42</v>
+        <v>220937.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-14.42</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.92</v>
+        <v>51.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.95</v>
+        <v>47.4</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>648147.4</v>
+        <v>609252.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>212611.62</v>
+        <v>218290.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>83071.93395825941</t>
+          <t>62824.50483930594</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.95</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,22 +4863,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.29</v>
+        <v>50.92</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.43</v>
+        <v>46.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>564572.4</v>
+        <v>648147.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>201223.44</v>
+        <v>212611.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>81925.83505825518</t>
+          <t>83071.93395825941</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13309.0</t>
+          <t>9872.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-11.36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>57.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>55.94</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.91</v>
+        <v>50.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.95</v>
+        <v>46.43</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-70.59</t>
+          <t>-62.98</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79712.98285714285</t>
+          <t>79808.1847360913</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>454356.8</v>
+        <v>564572.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>315081.5</t>
+          <t>357656.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>191580.74</v>
+        <v>201223.44</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>206916</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>17297.24955593463</t>
+          <t>27240.10886398395</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>78358.94966331136</t>
+          <t>81925.83505825518</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>797538.0</t>
+          <t>600689.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2851.548</t>
+          <t>3405.189</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-13.02</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>97.96</t>
+          <t>77.55</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>594.2</t>
+          <t>599.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>631.1</v>
+        <v>626.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>665.38</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>658.81</t>
+          <t>658.01</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-22.62</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-22.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-198.54</t>
+          <t>-198.33</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>2772989177.6</v>
+        <v>2528952699.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3103713833.7</t>
+          <t>3084050533.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>2209332488.54</v>
+        <v>2214399585.16</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-330724656</t>
+          <t>-555097833</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>159431909.2972355</t>
+          <t>124675711.092796</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-19624770.94642115</t>
+          <t>-66483379.03162146</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>611.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>612.0</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>619.0</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3697.739</t>
+          <t>2851.548</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.55</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.96</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>586.6</t>
+          <t>594.2</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>636</v>
+        <v>631.1</v>
       </c>
       <c r="AN14" t="n">
-        <v>667.3</v>
+        <v>665.38</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>659.49</t>
+          <t>658.81</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-22.86</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-197.45</t>
+          <t>-198.54</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2845492684.8</v>
+        <v>2772989177.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3254023064.0</t>
+          <t>3103713833.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>2250939639.92</v>
+        <v>2209332488.54</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-408530379</t>
+          <t>-330724656</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>191987669.3415367</t>
+          <t>159431909.2972355</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>80988449.20909452</t>
+          <t>-19624770.94642115</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3906.167</t>
+          <t>3697.739</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.42</t>
+          <t>-12.55</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>44.92</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>586.6</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>640.85</v>
+        <v>636</v>
       </c>
       <c r="AN15" t="n">
-        <v>668.88</v>
+        <v>667.3</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>660.11</t>
+          <t>659.49</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-32.16</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-193.67</t>
+          <t>-197.45</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>2895931468.2</v>
+        <v>2845492684.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3423927956.4</t>
+          <t>3254023064.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>2313304958.2</v>
+        <v>2250939639.92</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-527996488</t>
+          <t>-408530379</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>212169345.7292535</t>
+          <t>191987669.3415367</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>168000892.6023631</t>
+          <t>80988449.20909452</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>594.0</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>584.0</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7309.42</t>
+          <t>3906.167</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>-15.42</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.34</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>572.0</t>
+          <t>577.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>646.8</v>
+        <v>640.85</v>
       </c>
       <c r="AN16" t="n">
-        <v>670.4400000000001</v>
+        <v>668.88</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>660.9</t>
+          <t>660.11</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-32.16</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-29.38</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-19.98</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-186.14</t>
+          <t>-193.67</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3701315712</v>
+        <v>2895931468.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3406103963.5</t>
+          <t>3423927956.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>2315429027.54</v>
+        <v>2313304958.2</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>295211748</t>
+          <t>-527996488</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>220199973.5705063</t>
+          <t>212169345.7292535</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>280713247.2140913</t>
+          <t>168000892.6023631</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>580.0</t>
+          <t>589.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>593.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5705.448</t>
+          <t>7309.42</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>653.25</v>
+        <v>646.8</v>
       </c>
       <c r="AN17" t="n">
-        <v>671.96</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3639148367.2</v>
+        <v>3701315712</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>2279747515.3</v>
+        <v>2315429027.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>659.5</v>
+        <v>653.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>673.4</v>
+        <v>671.96</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3434438489.8</v>
+        <v>3639148367.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>2234436035.54</v>
+        <v>2279747515.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,209 +8324,209 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>673.4</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>3313286961.136947</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>3434438489.8</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2234436035.54</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>665.8</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>674.84</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>3313612064.535</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>3662553443.2</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2215412102.28</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>672.05</v>
+        <v>665.8</v>
       </c>
       <c r="AN20" t="n">
-        <v>676.22</v>
+        <v>674.84</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3951924444.6</v>
+        <v>3662553443.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>2193079344.64</v>
+        <v>2215412102.28</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>678.2</v>
+        <v>672.05</v>
       </c>
       <c r="AN21" t="n">
-        <v>677.46</v>
+        <v>676.22</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3110892215</v>
+        <v>3951924444.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2089597881.18</v>
+        <v>2193079344.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>272741488.1174035</t>
+          <t>504555995.9956522</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9654,33 +9654,33 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>681.95</v>
+        <v>678.2</v>
       </c>
       <c r="AN22" t="n">
-        <v>677.64</v>
+        <v>677.46</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>2660675287.2</v>
+        <v>3110892215</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2031062259.28</v>
+        <v>2089597881.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>184622942.8942842</t>
+          <t>272741488.1174035</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3558.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>647.4</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>684.55</v>
+        <v>681.95</v>
       </c>
       <c r="AN23" t="n">
-        <v>677.36</v>
+        <v>677.64</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>665.98</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-270.92</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-112.39</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3313612064.535</t>
+          <t>3313286961.136947</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>2688233856.6</v>
+        <v>2660675287.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>2395309044.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2012331643.46</v>
+        <v>2031062259.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>265366242</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>83340222.31716728</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>236195769.4007463</t>
+          <t>184622942.8942842</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>2253776059.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>446399</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1771.0</t>
+          <t>1130.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.96</t>
+          <t>-31.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>54.12</t>
+          <t>54.18000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>54.17</v>
+        <v>54.49</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.12</v>
+        <v>50.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-27.89</t>
+          <t>-31.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-44.62</t>
+          <t>-48.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>166065.8</v>
+        <v>134112.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>251474.7</t>
+          <t>196665.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>241154.9</v>
+        <v>241817.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-85408</t>
+          <t>-62552</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1009.327061166613</t>
+          <t>-5818.002838890967</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-36094.89205399787</t>
+          <t>-43368.31728920765</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2660.0</t>
+          <t>1771.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-33.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>53.82000000000001</t>
+          <t>54.12</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.79</v>
+        <v>54.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.76</v>
+        <v>50.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-27.89</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-44.62</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>206856.8</v>
+        <v>166065.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>301780.3</t>
+          <t>251474.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>239526.02</v>
+        <v>241154.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-94923</t>
+          <t>-85408</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7755.548718469247</t>
+          <t>1009.327061166613</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-28244.57414462682</t>
+          <t>-36094.89205399787</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2793.0</t>
+          <t>2660.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-40.68</t>
+          <t>-31.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>53.82000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.32</v>
+        <v>53.79</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.41</v>
+        <v>49.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-36.99</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>217717</v>
+        <v>206856.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>367044.8</t>
+          <t>301780.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>237158.66</v>
+        <v>239526.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-149327</t>
+          <t>-94923</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>14301.02560266853</t>
+          <t>7755.548718469247</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-21084.67091178865</t>
+          <t>-28244.57414462682</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3922.0</t>
+          <t>2793.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-44.99</t>
+          <t>-40.68</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.92</v>
+        <v>53.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.09</v>
+        <v>49.41</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-36.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>231160.8</v>
+        <v>217717</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>420206.6</t>
+          <t>367044.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>235339.22</v>
+        <v>237158.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-189045</t>
+          <t>-149327</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20734.78860529711</t>
+          <t>14301.02560266853</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10587.49947517022</t>
+          <t>-21084.67091178865</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4120.0</t>
+          <t>3922.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,72 +2618,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-44.99</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-42.86</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.18000000000001</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.64</v>
+        <v>52.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.75</v>
+        <v>49.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-31.48</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>259217.6</v>
+        <v>231160.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>453682.5</t>
+          <t>420206.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>233052.36</v>
+        <v>235339.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-194464</t>
+          <t>-189045</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>26429.75007447299</t>
+          <t>20734.78860529711</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2426.165298745036</t>
+          <t>-10587.49947517022</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.53</v>
+        <v>52.64</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.48</v>
+        <v>48.75</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>336883.6</v>
+        <v>259217.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>229641.16</v>
+        <v>233052.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.4</v>
+        <v>52.53</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.2</v>
+        <v>48.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>396703.8</v>
+        <v>336883.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>224069.9</v>
+        <v>229641.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>51.93</v>
+        <v>52.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>516372.6</v>
+        <v>396703.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>220937.42</v>
+        <v>224069.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>51.44</v>
+        <v>51.93</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>609252.4</v>
+        <v>516372.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>218290.42</v>
+        <v>220937.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-12.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.92</v>
+        <v>51.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.95</v>
+        <v>47.4</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>648147.4</v>
+        <v>609252.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>212611.62</v>
+        <v>218290.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>83071.93395825941</t>
+          <t>62824.50483930594</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9872.0</t>
+          <t>9666.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>-16.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>64.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,33 +5293,33 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>55.94</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.29</v>
+        <v>50.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.43</v>
+        <v>46.95</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>78.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-62.98</t>
+          <t>-53.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79808.1847360913</t>
+          <t>79826.74572649573</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>564572.4</v>
+        <v>648147.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>357656.0</t>
+          <t>393131.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>201223.44</v>
+        <v>212611.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>27240.10886398395</t>
+          <t>35829.6204169494</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>81925.83505825518</t>
+          <t>83071.93395825941</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>600689.0</t>
+          <t>609988.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>62.23</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3405.189</t>
+          <t>2335.806</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-18.00</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.02</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>77.55</t>
+          <t>80.43</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>85.31</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>599.8</t>
+          <t>603.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>626.3</v>
+        <v>621.9</v>
       </c>
       <c r="AN13" t="n">
-        <v>663.5599999999999</v>
+        <v>661.92</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>658.01</t>
+          <t>657.1</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-22.62</t>
+          <t>-21.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-22.81</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-198.33</t>
+          <t>-196.97</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>2528952699.4</v>
+        <v>1955657888.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3084050533.3</t>
+          <t>2828486800.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>2214399585.16</v>
+        <v>2204685972.04</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-555097833</t>
+          <t>-872828911</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>124675711.092796</t>
+          <t>83077517.50306264</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-66483379.03162146</t>
+          <t>-145712547.2404709</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2851.548</t>
+          <t>3405.189</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-13.02</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>97.96</t>
+          <t>77.55</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>594.2</t>
+          <t>599.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>631.1</v>
+        <v>626.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>665.38</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>658.81</t>
+          <t>658.01</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-22.62</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-22.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-198.54</t>
+          <t>-198.33</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2772989177.6</v>
+        <v>2528952699.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3103713833.7</t>
+          <t>3084050533.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>2209332488.54</v>
+        <v>2214399585.16</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-330724656</t>
+          <t>-555097833</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>159431909.2972355</t>
+          <t>124675711.092796</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-19624770.94642115</t>
+          <t>-66483379.03162146</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>611.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
           <t>612.0</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>619.0</t>
-        </is>
-      </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3697.739</t>
+          <t>2851.548</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-12.55</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.96</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>586.6</t>
+          <t>594.2</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>636</v>
+        <v>631.1</v>
       </c>
       <c r="AN15" t="n">
-        <v>667.3</v>
+        <v>665.38</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>659.49</t>
+          <t>658.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-22.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-197.45</t>
+          <t>-198.54</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>2845492684.8</v>
+        <v>2772989177.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3254023064.0</t>
+          <t>3103713833.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>2250939639.92</v>
+        <v>2209332488.54</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-408530379</t>
+          <t>-330724656</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>191987669.3415367</t>
+          <t>159431909.2972355</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>80988449.20909452</t>
+          <t>-19624770.94642115</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3906.167</t>
+          <t>3697.739</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.42</t>
+          <t>-12.55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>44.92</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>586.6</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>640.85</v>
+        <v>636</v>
       </c>
       <c r="AN16" t="n">
-        <v>668.88</v>
+        <v>667.3</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>660.11</t>
+          <t>659.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-32.16</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-193.67</t>
+          <t>-197.45</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>2895931468.2</v>
+        <v>2845492684.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3423927956.4</t>
+          <t>3254023064.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>2313304958.2</v>
+        <v>2250939639.92</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-527996488</t>
+          <t>-408530379</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>212169345.7292535</t>
+          <t>191987669.3415367</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>168000892.6023631</t>
+          <t>80988449.20909452</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>594.0</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>584.0</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7309.42</t>
+          <t>3906.167</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>-15.42</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.34</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>572.0</t>
+          <t>577.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>646.8</v>
+        <v>640.85</v>
       </c>
       <c r="AN17" t="n">
-        <v>670.4400000000001</v>
+        <v>668.88</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>660.9</t>
+          <t>660.11</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-32.16</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-29.38</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-19.98</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-186.14</t>
+          <t>-193.67</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3701315712</v>
+        <v>2895931468.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3406103963.5</t>
+          <t>3423927956.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>2315429027.54</v>
+        <v>2313304958.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>295211748</t>
+          <t>-527996488</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>220199973.5705063</t>
+          <t>212169345.7292535</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>280713247.2140913</t>
+          <t>168000892.6023631</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>580.0</t>
+          <t>589.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>593.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5705.448</t>
+          <t>7309.42</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>653.25</v>
+        <v>646.8</v>
       </c>
       <c r="AN18" t="n">
-        <v>671.96</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3639148367.2</v>
+        <v>3701315712</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>2279747515.3</v>
+        <v>2315429027.54</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>659.5</v>
+        <v>653.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>673.4</v>
+        <v>671.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3434438489.8</v>
+        <v>3639148367.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>2234436035.54</v>
+        <v>2279747515.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,209 +8754,209 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>673.4</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>3311592692.021368</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>3434438489.8</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2234436035.54</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM20" t="n">
-        <v>665.8</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>674.84</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>3313286961.136947</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>3662553443.2</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2215412102.28</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>672.05</v>
+        <v>665.8</v>
       </c>
       <c r="AN21" t="n">
-        <v>676.22</v>
+        <v>674.84</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3951924444.6</v>
+        <v>3662553443.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2193079344.64</v>
+        <v>2215412102.28</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>678.2</v>
+        <v>672.05</v>
       </c>
       <c r="AN22" t="n">
-        <v>677.46</v>
+        <v>676.22</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3110892215</v>
+        <v>3951924444.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2089597881.18</v>
+        <v>2193079344.64</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>272741488.1174035</t>
+          <t>504555995.9956522</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10084,33 +10084,33 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>636.8</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>681.95</v>
+        <v>678.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>677.64</v>
+        <v>677.46</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>665.81</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-175.57</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-122.08</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3313286961.136947</t>
+          <t>3311592692.021368</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>2660675287.2</v>
+        <v>3110892215</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>2577610128.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2031062259.28</v>
+        <v>2089597881.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>533282086</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>112478878.5941267</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>184622942.8942842</t>
+          <t>272741488.1174035</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>3971577357.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>447884</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1130.0</t>
+          <t>1352.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.81</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,29 +1058,29 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>54.49</v>
+        <v>54.87</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.46</v>
+        <v>50.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.93</t>
+          <t>-31.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-48.72</t>
+          <t>-52.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>61892.0</t>
+          <t>74300.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>134112.6</v>
+        <v>105626.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>196665.1</t>
+          <t>168393.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>241817.16</v>
+        <v>242999.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-62552</t>
+          <t>-62767</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5818.002838890967</t>
+          <t>-12068.29579008071</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-43368.31728920765</t>
+          <t>-46444.90702162433</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>61892.0</t>
+          <t>74300.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1771.0</t>
+          <t>1130.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-33.96</t>
+          <t>-31.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>54.12</t>
+          <t>54.18000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>54.17</v>
+        <v>54.49</v>
       </c>
       <c r="AN3" t="n">
-        <v>50.12</v>
+        <v>50.46</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-27.89</t>
+          <t>-31.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-44.62</t>
+          <t>-48.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>166065.8</v>
+        <v>134112.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>251474.7</t>
+          <t>196665.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>241154.9</v>
+        <v>241817.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-85408</t>
+          <t>-62552</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1009.327061166613</t>
+          <t>-5818.002838890967</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-36094.89205399787</t>
+          <t>-43368.31728920765</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2660.0</t>
+          <t>1771.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-33.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,211 +1874,211 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>8.08</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>54.12</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>45.88</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-27.89</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-44.62</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>79871.72901849219</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>97633.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>166065.8</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>251474.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>241154.9</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-85408</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1009.327061166613</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-36094.89205399787</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>97633.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>41.27</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>鑫聯大投控</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>鑫聯大投控</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-4.142025122335156</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>31.9210612054922</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>52.5841306079603</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
           <t>1.82</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>8.97</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>53.82000000000001</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>53.79</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>49.76</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>45.67</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-25.44</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-40.76</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>79826.74572649573</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>144893.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>206856.8</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>301780.3</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>239526.02</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-94923</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>7755.548718469247</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-28244.57414462682</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>144893.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>41.79</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>鑫聯大投控</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>鑫聯大投控</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-4.142025122335156</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>31.9210612054922</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>52.5841306079603</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BU4" t="inlineStr">
         <is>
           <t>77.26</t>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2793.0</t>
+          <t>2660.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-40.68</t>
+          <t>-31.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>53.82000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.32</v>
+        <v>53.79</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.41</v>
+        <v>49.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-36.99</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>217717</v>
+        <v>206856.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>367044.8</t>
+          <t>301780.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>237158.66</v>
+        <v>239526.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-149327</t>
+          <t>-94923</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>14301.02560266853</t>
+          <t>7755.548718469247</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-21084.67091178865</t>
+          <t>-28244.57414462682</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3922.0</t>
+          <t>2793.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-44.99</t>
+          <t>-40.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.92</v>
+        <v>53.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.09</v>
+        <v>49.41</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-36.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>231160.8</v>
+        <v>217717</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>420206.6</t>
+          <t>367044.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>235339.22</v>
+        <v>237158.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-189045</t>
+          <t>-149327</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20734.78860529711</t>
+          <t>14301.02560266853</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10587.49947517022</t>
+          <t>-21084.67091178865</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4120.0</t>
+          <t>3922.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,72 +3048,72 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-44.99</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-42.86</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.18000000000001</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.64</v>
+        <v>52.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.75</v>
+        <v>49.09</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-31.48</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>259217.6</v>
+        <v>231160.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>453682.5</t>
+          <t>420206.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>233052.36</v>
+        <v>235339.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-194464</t>
+          <t>-189045</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>26429.75007447299</t>
+          <t>20734.78860529711</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2426.165298745036</t>
+          <t>-10587.49947517022</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,14 +3446,14 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.53</v>
+        <v>52.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.48</v>
+        <v>48.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>336883.6</v>
+        <v>259217.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>229641.16</v>
+        <v>233052.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.4</v>
+        <v>52.53</v>
       </c>
       <c r="AN9" t="n">
-        <v>48.2</v>
+        <v>48.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>396703.8</v>
+        <v>336883.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>224069.9</v>
+        <v>229641.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>51.93</v>
+        <v>52.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>516372.6</v>
+        <v>396703.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>220937.42</v>
+        <v>224069.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.41</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>51.44</v>
+        <v>51.93</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>609252.4</v>
+        <v>516372.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>218290.42</v>
+        <v>220937.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9666.0</t>
+          <t>5798.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-16.11</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>64.87</t>
+          <t>45.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.92</v>
+        <v>51.44</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.95</v>
+        <v>47.4</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-53.87</t>
+          <t>-45.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79826.74572649573</t>
+          <t>79871.72901849219</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>648147.4</v>
+        <v>609252.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>393131.5</t>
+          <t>418153.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>212611.62</v>
+        <v>218290.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>191098</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35829.6204169494</t>
+          <t>39982.67955885041</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>83071.93395825941</t>
+          <t>62824.50483930594</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>609988.0</t>
+          <t>357016.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2335.806</t>
+          <t>2028.846</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>603.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-24.92</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>80.43</t>
+          <t>87.18</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>85.31</t>
+          <t>81.72</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>603.4</t>
+          <t>606.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>621.9</v>
+        <v>617.85</v>
       </c>
       <c r="AN13" t="n">
-        <v>661.92</v>
+        <v>660.6</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>657.1</t>
+          <t>656.19</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-21.91</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-196.97</t>
+          <t>-194.46</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1415940028.0</t>
+          <t>1228596935.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>1955657888.8</v>
+        <v>1740579212.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2828486800.4</t>
+          <t>2318255340.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>2204685972.04</v>
+        <v>2189722054.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-872828911</t>
+          <t>-577676127</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>83077517.50306264</t>
+          <t>37745455.84402931</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-145712547.2404709</t>
+          <t>-211580883.280654</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1415940028.0</t>
+          <t>1228596935.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>608.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>603.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3405.189</t>
+          <t>2335.806</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-18.00</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.02</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>77.55</t>
+          <t>80.43</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>85.31</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>599.8</t>
+          <t>603.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>626.3</v>
+        <v>621.9</v>
       </c>
       <c r="AN14" t="n">
-        <v>663.5599999999999</v>
+        <v>661.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>658.01</t>
+          <t>657.1</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-22.62</t>
+          <t>-21.23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-22.81</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-198.33</t>
+          <t>-196.97</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2528952699.4</v>
+        <v>1955657888.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3084050533.3</t>
+          <t>2828486800.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>2214399585.16</v>
+        <v>2204685972.04</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-555097833</t>
+          <t>-872828911</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>124675711.092796</t>
+          <t>83077517.50306264</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-66483379.03162146</t>
+          <t>-145712547.2404709</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2851.548</t>
+          <t>3405.189</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-13.02</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>97.96</t>
+          <t>77.55</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>594.2</t>
+          <t>599.8</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>631.1</v>
+        <v>626.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>665.38</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>658.81</t>
+          <t>658.01</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-22.62</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-22.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-198.54</t>
+          <t>-198.33</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>2772989177.6</v>
+        <v>2528952699.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3103713833.7</t>
+          <t>3084050533.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>2209332488.54</v>
+        <v>2214399585.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-330724656</t>
+          <t>-555097833</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>159431909.2972355</t>
+          <t>124675711.092796</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-19624770.94642115</t>
+          <t>-66483379.03162146</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6796,17 +6796,17 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>611.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
           <t>612.0</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>619.0</t>
-        </is>
-      </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3697.739</t>
+          <t>2851.548</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-12.55</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.96</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>586.6</t>
+          <t>594.2</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>636</v>
+        <v>631.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>667.3</v>
+        <v>665.38</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>659.49</t>
+          <t>658.81</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-22.86</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-197.45</t>
+          <t>-198.54</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>2845492684.8</v>
+        <v>2772989177.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3254023064.0</t>
+          <t>3103713833.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>2250939639.92</v>
+        <v>2209332488.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-408530379</t>
+          <t>-330724656</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>191987669.3415367</t>
+          <t>159431909.2972355</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>80988449.20909452</t>
+          <t>-19624770.94642115</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3906.167</t>
+          <t>3697.739</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.42</t>
+          <t>-12.55</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>44.92</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>586.6</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>640.85</v>
+        <v>636</v>
       </c>
       <c r="AN17" t="n">
-        <v>668.88</v>
+        <v>667.3</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>660.11</t>
+          <t>659.49</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-32.16</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-193.67</t>
+          <t>-197.45</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>2895931468.2</v>
+        <v>2845492684.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3423927956.4</t>
+          <t>3254023064.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>2313304958.2</v>
+        <v>2250939639.92</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-527996488</t>
+          <t>-408530379</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>212169345.7292535</t>
+          <t>191987669.3415367</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>168000892.6023631</t>
+          <t>80988449.20909452</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>594.0</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>584.0</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7309.42</t>
+          <t>3906.167</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>-15.42</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.34</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>572.0</t>
+          <t>577.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>646.8</v>
+        <v>640.85</v>
       </c>
       <c r="AN18" t="n">
-        <v>670.4400000000001</v>
+        <v>668.88</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>660.9</t>
+          <t>660.11</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-32.16</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-29.38</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-19.98</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-186.14</t>
+          <t>-193.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3701315712</v>
+        <v>2895931468.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3406103963.5</t>
+          <t>3423927956.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>2315429027.54</v>
+        <v>2313304958.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>295211748</t>
+          <t>-527996488</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>220199973.5705063</t>
+          <t>212169345.7292535</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>280713247.2140913</t>
+          <t>168000892.6023631</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>580.0</t>
+          <t>589.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>593.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5705.448</t>
+          <t>7309.42</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>653.25</v>
+        <v>646.8</v>
       </c>
       <c r="AN19" t="n">
-        <v>671.96</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3639148367.2</v>
+        <v>3701315712</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>2279747515.3</v>
+        <v>2315429027.54</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>659.5</v>
+        <v>653.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>673.4</v>
+        <v>671.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3434438489.8</v>
+        <v>3639148367.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>2234436035.54</v>
+        <v>2279747515.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9053,42 +9053,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3669.211</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>573.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.53</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>4407.34</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>566.0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>6.14</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,209 +9184,209 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>673.4</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>3309503506.687767</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>3434438489.8</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2234436035.54</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>665.8</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>674.84</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>3311592692.021368</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>3662553443.2</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2215412102.28</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>672.05</v>
+        <v>665.8</v>
       </c>
       <c r="AN22" t="n">
-        <v>676.22</v>
+        <v>674.84</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3951924444.6</v>
+        <v>3662553443.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2193079344.64</v>
+        <v>2215412102.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>10997.319</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>50.83</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>617.2</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>678.2</v>
+        <v>672.05</v>
       </c>
       <c r="AN23" t="n">
-        <v>677.46</v>
+        <v>676.22</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>664.88</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-149.52</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-20.41</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-135.26</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3311592692.021368</t>
+          <t>3309503506.687767</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3110892215</v>
+        <v>3951924444.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>3034497195.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2089597881.18</v>
+        <v>2193079344.64</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>917427249</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>172798435.1174383</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>272741488.1174035</t>
+          <t>504555995.9956522</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>6330911536.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>447884</t>
+          <t>450855</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1352.0</t>
+          <t>1902.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,211 +1014,211 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>54.18000000000001</t>
+          <t>54.76000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>54.87</v>
+        <v>55.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.8</v>
+        <v>51.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.31</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-55.67</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>79983.96946022728</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>105926.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>96928.8</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>157322.9</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>242300</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-60394</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-17144.78061603374</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-45065.44715877538</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>105926.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>43.34</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>鑫聯大投控</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>鑫聯大投控</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-4.142025122335156</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>31.9210612054922</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>52.5841306079603</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-52.44</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>79871.72901849219</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>74300.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>105626.2</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>168393.5</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>242999.08</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-62767</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-12068.29579008071</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-46444.90702162433</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>74300.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>42.30</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>鑫聯大投控</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>鑫聯大投控</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-4.142025122335156</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>31.9210612054922</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>52.5841306079603</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
       <c r="BU2" t="inlineStr">
         <is>
           <t>77.26</t>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1130.0</t>
+          <t>1352.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.81</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,42 +1444,42 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>54.49</v>
+        <v>54.87</v>
       </c>
       <c r="AN3" t="n">
-        <v>50.46</v>
+        <v>50.8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.93</t>
+          <t>-31.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-48.72</t>
+          <t>-52.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>61892.0</t>
+          <t>74300.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>134112.6</v>
+        <v>105626.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>196665.1</t>
+          <t>168393.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>241817.16</v>
+        <v>242999.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-62552</t>
+          <t>-62767</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5818.002838890967</t>
+          <t>-12068.29579008071</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-43368.31728920765</t>
+          <t>-46444.90702162433</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>61892.0</t>
+          <t>74300.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1771.0</t>
+          <t>1130.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.96</t>
+          <t>-31.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>54.12</t>
+          <t>54.18000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>54.17</v>
+        <v>54.49</v>
       </c>
       <c r="AN4" t="n">
-        <v>50.12</v>
+        <v>50.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-27.89</t>
+          <t>-31.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-44.62</t>
+          <t>-48.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>166065.8</v>
+        <v>134112.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>251474.7</t>
+          <t>196665.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>241154.9</v>
+        <v>241817.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-85408</t>
+          <t>-62552</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1009.327061166613</t>
+          <t>-5818.002838890967</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-36094.89205399787</t>
+          <t>-43368.31728920765</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2660.0</t>
+          <t>1771.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-33.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>53.82000000000001</t>
+          <t>54.12</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.79</v>
+        <v>54.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.76</v>
+        <v>50.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-27.89</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-44.62</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>206856.8</v>
+        <v>166065.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>301780.3</t>
+          <t>251474.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>239526.02</v>
+        <v>241154.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-94923</t>
+          <t>-85408</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7755.548718469247</t>
+          <t>1009.327061166613</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-28244.57414462682</t>
+          <t>-36094.89205399787</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2793.0</t>
+          <t>2660.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-40.68</t>
+          <t>-31.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>53.82000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.32</v>
+        <v>53.79</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.41</v>
+        <v>49.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-36.99</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>217717</v>
+        <v>206856.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>367044.8</t>
+          <t>301780.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>237158.66</v>
+        <v>239526.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-149327</t>
+          <t>-94923</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>14301.02560266853</t>
+          <t>7755.548718469247</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-21084.67091178865</t>
+          <t>-28244.57414462682</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3922.0</t>
+          <t>2793.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-44.99</t>
+          <t>-40.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.92</v>
+        <v>53.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>49.09</v>
+        <v>49.41</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-36.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>231160.8</v>
+        <v>217717</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>420206.6</t>
+          <t>367044.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>235339.22</v>
+        <v>237158.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-189045</t>
+          <t>-149327</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20734.78860529711</t>
+          <t>14301.02560266853</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10587.49947517022</t>
+          <t>-21084.67091178865</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4120.0</t>
+          <t>3922.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,72 +3478,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-44.99</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-42.86</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.18000000000001</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.64</v>
+        <v>52.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.75</v>
+        <v>49.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-31.48</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>259217.6</v>
+        <v>231160.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>453682.5</t>
+          <t>420206.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>233052.36</v>
+        <v>235339.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-194464</t>
+          <t>-189045</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>26429.75007447299</t>
+          <t>20734.78860529711</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2426.165298745036</t>
+          <t>-10587.49947517022</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>221658.0</t>
+          <t>216732.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5560.0</t>
+          <t>4120.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.26</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>57.18000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.53</v>
+        <v>52.64</v>
       </c>
       <c r="AN9" t="n">
-        <v>48.48</v>
+        <v>48.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-31.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>336883.6</v>
+        <v>259217.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>450728.0</t>
+          <t>453682.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>229641.16</v>
+        <v>233052.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-113844</t>
+          <t>-194464</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>31676.28014233082</t>
+          <t>26429.75007447299</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>8791.746571103286</t>
+          <t>-2426.165298745036</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>301588.0</t>
+          <t>221658.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>5560.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.4</v>
+        <v>52.53</v>
       </c>
       <c r="AN10" t="n">
-        <v>48.2</v>
+        <v>48.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>396703.8</v>
+        <v>336883.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>425530.3</t>
+          <t>450728.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>224069.9</v>
+        <v>229641.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-28826</t>
+          <t>-113844</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>35837.10442800855</t>
+          <t>31676.28014233082</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>15939.41543620441</t>
+          <t>8791.746571103286</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>199194.0</t>
+          <t>301588.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>52.65</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3633.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>79.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.77999999999999</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>51.93</v>
+        <v>52.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-38.05</t>
+          <t>-32.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>516372.6</v>
+        <v>396703.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>418795.8</t>
+          <t>425530.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>220937.42</v>
+        <v>224069.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>-28826</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>39454.86606288203</t>
+          <t>35837.10442800855</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>36551.8918350559</t>
+          <t>15939.41543620441</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>216632.0</t>
+          <t>199194.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>52.65</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5798.0</t>
+          <t>3633.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>45.70</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>79.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>95.78</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>60.77999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>51.44</v>
+        <v>51.93</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-45.25</t>
+          <t>-38.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79871.72901849219</t>
+          <t>79983.96946022728</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>609252.4</v>
+        <v>516372.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>418153.5</t>
+          <t>418795.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>218290.42</v>
+        <v>220937.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>191098</t>
+          <t>97576</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>39982.67955885041</t>
+          <t>39454.86606288203</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>62824.50483930594</t>
+          <t>36551.8918350559</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>357016.0</t>
+          <t>216632.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>53.69</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d】;【x】看好</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2028.846</t>
+          <t>3544.654</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-24.92</t>
+          <t>-24.43</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>87.18</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>81.72</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>606.8</t>
+          <t>607.6</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>617.85</v>
+        <v>614.6</v>
       </c>
       <c r="AN13" t="n">
-        <v>660.6</v>
+        <v>659.3200000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>656.19</t>
+          <t>655.36</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-21.91</t>
+          <t>-21.00</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-194.46</t>
+          <t>-190.52</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1228596935.0</t>
+          <t>2188815486.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>1740579212.4</v>
+        <v>1727980973.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2318255340.3</t>
+          <t>2286736829.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>2189722054.78</v>
+        <v>2197511210.52</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-577676127</t>
+          <t>-558755855</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>37745455.84402931</t>
+          <t>4187261.852368519</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-211580883.280654</t>
+          <t>-180382805.1017659</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1228596935.0</t>
+          <t>2188815486.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>622.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>607.0</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>608.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2335.806</t>
+          <t>2028.846</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>603.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-24.92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>80.43</t>
+          <t>87.18</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>85.31</t>
+          <t>81.72</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>603.4</t>
+          <t>606.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>621.9</v>
+        <v>617.85</v>
       </c>
       <c r="AN14" t="n">
-        <v>661.92</v>
+        <v>660.6</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>657.1</t>
+          <t>656.19</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-21.91</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-196.97</t>
+          <t>-194.46</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1415940028.0</t>
+          <t>1228596935.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>1955657888.8</v>
+        <v>1740579212.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2828486800.4</t>
+          <t>2318255340.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>2204685972.04</v>
+        <v>2189722054.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-872828911</t>
+          <t>-577676127</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>83077517.50306264</t>
+          <t>37745455.84402931</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-145712547.2404709</t>
+          <t>-211580883.280654</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1415940028.0</t>
+          <t>1228596935.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>608.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>603.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3405.189</t>
+          <t>2335.806</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-18.00</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.02</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>77.55</t>
+          <t>80.43</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>85.31</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>599.8</t>
+          <t>603.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>626.3</v>
+        <v>621.9</v>
       </c>
       <c r="AN15" t="n">
-        <v>663.5599999999999</v>
+        <v>661.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>658.01</t>
+          <t>657.1</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-22.62</t>
+          <t>-21.23</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-22.81</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-198.33</t>
+          <t>-196.97</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>2528952699.4</v>
+        <v>1955657888.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3084050533.3</t>
+          <t>2828486800.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>2214399585.16</v>
+        <v>2204685972.04</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-555097833</t>
+          <t>-872828911</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>124675711.092796</t>
+          <t>83077517.50306264</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-66483379.03162146</t>
+          <t>-145712547.2404709</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2851.548</t>
+          <t>3405.189</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-13.02</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>97.96</t>
+          <t>77.55</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>594.2</t>
+          <t>599.8</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>631.1</v>
+        <v>626.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>665.38</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>658.81</t>
+          <t>658.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-22.62</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-22.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-198.54</t>
+          <t>-198.33</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>2772989177.6</v>
+        <v>2528952699.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3103713833.7</t>
+          <t>3084050533.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>2209332488.54</v>
+        <v>2214399585.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-330724656</t>
+          <t>-555097833</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>159431909.2972355</t>
+          <t>124675711.092796</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-19624770.94642115</t>
+          <t>-66483379.03162146</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7226,17 +7226,17 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>611.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>612.0</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>619.0</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3697.739</t>
+          <t>2851.548</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-12.55</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.96</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>586.6</t>
+          <t>594.2</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>636</v>
+        <v>631.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>667.3</v>
+        <v>665.38</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>659.49</t>
+          <t>658.81</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-22.86</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-197.45</t>
+          <t>-198.54</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>2845492684.8</v>
+        <v>2772989177.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3254023064.0</t>
+          <t>3103713833.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>2250939639.92</v>
+        <v>2209332488.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-408530379</t>
+          <t>-330724656</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>191987669.3415367</t>
+          <t>159431909.2972355</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>80988449.20909452</t>
+          <t>-19624770.94642115</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3906.167</t>
+          <t>3697.739</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-15.42</t>
+          <t>-12.55</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>44.92</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>586.6</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>640.85</v>
+        <v>636</v>
       </c>
       <c r="AN18" t="n">
-        <v>668.88</v>
+        <v>667.3</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>660.11</t>
+          <t>659.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-32.16</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-193.67</t>
+          <t>-197.45</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>2895931468.2</v>
+        <v>2845492684.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3423927956.4</t>
+          <t>3254023064.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>2313304958.2</v>
+        <v>2250939639.92</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-527996488</t>
+          <t>-408530379</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>212169345.7292535</t>
+          <t>191987669.3415367</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>168000892.6023631</t>
+          <t>80988449.20909452</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>594.0</t>
         </is>
       </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>584.0</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7309.42</t>
+          <t>3906.167</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>-15.42</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.34</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>572.0</t>
+          <t>577.4</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>646.8</v>
+        <v>640.85</v>
       </c>
       <c r="AN19" t="n">
-        <v>670.4400000000001</v>
+        <v>668.88</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>660.9</t>
+          <t>660.11</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-32.16</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-29.38</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-19.98</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-186.14</t>
+          <t>-193.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3701315712</v>
+        <v>2895931468.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3406103963.5</t>
+          <t>3423927956.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>2315429027.54</v>
+        <v>2313304958.2</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>295211748</t>
+          <t>-527996488</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>220199973.5705063</t>
+          <t>212169345.7292535</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>280713247.2140913</t>
+          <t>168000892.6023631</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>4282414081.0</t>
+          <t>2303990317.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>580.0</t>
+          <t>589.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>593.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>585.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5705.448</t>
+          <t>7309.42</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-15.34</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>577.0</t>
+          <t>572.0</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>653.25</v>
+        <v>646.8</v>
       </c>
       <c r="AN20" t="n">
-        <v>671.96</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>661.72</t>
+          <t>660.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-66.10</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-29.38</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>-19.98</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-176.01</t>
+          <t>-186.14</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3639148367.2</v>
+        <v>3701315712</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3149911827.2</t>
+          <t>3406103963.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>2279747515.3</v>
+        <v>2315429027.54</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>489236540</t>
+          <t>295211748</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>209197560.1807636</t>
+          <t>220199973.5705063</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>219731448.8303423</t>
+          <t>280713247.2140913</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>3277325446.0</t>
+          <t>4282414081.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>559.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>583.0</t>
+          <t>593.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>585.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3669.211</t>
+          <t>5705.448</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-10.69</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>577.0</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>659.5</v>
+        <v>653.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>673.4</v>
+        <v>671.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>662.84</t>
+          <t>661.72</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-66.10</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-29.29</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-163.45</t>
+          <t>-176.01</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3434438489.8</v>
+        <v>3639148367.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3061336173.2</t>
+          <t>3149911827.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2234436035.54</v>
+        <v>2279747515.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>373102316</t>
+          <t>489236540</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>207282307.699022</t>
+          <t>209197560.1807636</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>232455110.2881894</t>
+          <t>219731448.8303423</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2111926901.0</t>
+          <t>3277325446.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4407.34</t>
+          <t>3669.211</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,209 +9614,209 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-10.69</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>673.4</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>662.84</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-86.99</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-27.53</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-14.72</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-163.45</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>3309466176.747869</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>3434438489.8</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>3061336173.2</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2234436035.54</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>373102316</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>207282307.699022</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>232455110.2881894</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>665.8</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>674.84</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>663.86</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-115.93</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-24.87</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-11.52</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-149.65</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>3309503506.687767</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>3662553443.2</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>3053660242.7</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2215412102.28</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>608893200</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>202705434.5009916</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>367193931.1105347</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>2504000596.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/09/17</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-19.69180399575732</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>32.8429209193585</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>24.67740643280432</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>583.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>562.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>566.0</t>
+          <t>573.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10997.319</t>
+          <t>4407.34</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.09</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>617.2</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>672.05</v>
+        <v>665.8</v>
       </c>
       <c r="AN23" t="n">
-        <v>676.22</v>
+        <v>674.84</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>664.88</t>
+          <t>663.86</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-149.52</t>
+          <t>-115.93</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-20.41</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-135.26</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>3309503506.687767</t>
+          <t>3309466176.747869</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3951924444.6</v>
+        <v>3662553443.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3034497195.4</t>
+          <t>3053660242.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2193079344.64</v>
+        <v>2215412102.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>917427249</t>
+          <t>608893200</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>172798435.1174383</t>
+          <t>202705434.5009916</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>504555995.9956522</t>
+          <t>367193931.1105347</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>6330911536.0</t>
+          <t>2504000596.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>450855</t>
+          <t>457540</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>562.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>566.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光碟機.xlsx
+++ b/Result/checksun_type/光碟機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1902.0</t>
+          <t>2713.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-35.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>54.76000000000001</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>55.2</v>
+        <v>55.68</v>
       </c>
       <c r="AN2" t="n">
-        <v>51.12</v>
+        <v>51.47</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-20.78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-55.67</t>
+          <t>-57.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79983.96946022728</t>
+          <t>80193.23191489362</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>105926.0</t>
+          <t>151676.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>96928.8</v>
+        <v>98285.39999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>157322.9</t>
+          <t>152571.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>242300</v>
+        <v>243137.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-60394</t>
+          <t>-54285</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-17144.78061603374</t>
+          <t>-20590.49730215344</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-45065.44715877538</t>
+          <t>-39541.93907581174</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>105926.0</t>
+          <t>151676.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t